--- a/database/event/2130/event_2130_evp_summary.xlsx
+++ b/database/event/2130/event_2130_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.1726</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9198</v>
+        <v>2.8511</v>
       </c>
       <c r="E2" t="n">
         <v>8.2707</v>
@@ -548,7 +548,7 @@
         <v>2.9469</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6821</v>
+        <v>2.6167</v>
       </c>
       <c r="E3" t="n">
         <v>7.6823</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.9646</v>
+        <v>6.0876</v>
       </c>
       <c r="C4" t="n">
-        <v>2.288</v>
+        <v>2.3352</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9882</v>
+        <v>1.9814</v>
       </c>
       <c r="E4" t="n">
-        <v>5.9646</v>
+        <v>6.0876</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6975</v>
+        <v>1.8205</v>
       </c>
       <c r="G4" t="n">
         <v>4.2671</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6975</v>
+        <v>1.8205</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3759</v>
+        <v>1.4756</v>
       </c>
       <c r="J4" t="n">
         <v>4.2671</v>
@@ -621,7 +621,7 @@
         <v>225</v>
       </c>
       <c r="M4" t="n">
-        <v>5.643</v>
+        <v>5.7427</v>
       </c>
       <c r="N4" t="n">
         <v>276</v>
@@ -640,7 +640,7 @@
         <v>1.9595</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6422</v>
+        <v>1.5912</v>
       </c>
       <c r="E5" t="n">
         <v>5.1082</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.066</v>
+        <v>4.0908</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5597</v>
+        <v>1.5692</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2212</v>
+        <v>1.1859</v>
       </c>
       <c r="E6" t="n">
-        <v>4.066</v>
+        <v>4.0908</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7228</v>
+        <v>3.7476</v>
       </c>
       <c r="G6" t="n">
         <v>0.3432</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7228</v>
+        <v>3.7476</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0175</v>
+        <v>3.0375</v>
       </c>
       <c r="J6" t="n">
         <v>0.3432</v>
@@ -713,7 +713,7 @@
         <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3607</v>
+        <v>3.3807</v>
       </c>
       <c r="N6" t="n">
         <v>184</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5199</v>
+        <v>3.7734</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3502</v>
+        <v>1.4475</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0006</v>
+        <v>1.0594</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5199</v>
+        <v>3.7734</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8875</v>
+        <v>1.141</v>
       </c>
       <c r="G7" t="n">
         <v>2.6324</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8875</v>
+        <v>1.141</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7194</v>
+        <v>0.9248</v>
       </c>
       <c r="J7" t="n">
         <v>2.6324</v>
@@ -759,7 +759,7 @@
         <v>225</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3518</v>
+        <v>3.5572</v>
       </c>
       <c r="N7" t="n">
         <v>276</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.9985</v>
+        <v>3.3749</v>
       </c>
       <c r="C8" t="n">
-        <v>1.1502</v>
+        <v>1.2946</v>
       </c>
       <c r="D8" t="n">
-        <v>0.79</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>2.9985</v>
+        <v>3.3749</v>
       </c>
       <c r="F8" t="n">
-        <v>2.1149</v>
+        <v>2.4913</v>
       </c>
       <c r="G8" t="n">
         <v>0.8836000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.1149</v>
+        <v>2.4913</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7142</v>
+        <v>2.0193</v>
       </c>
       <c r="J8" t="n">
         <v>0.8836000000000001</v>
@@ -805,7 +805,7 @@
         <v>225</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5978</v>
+        <v>2.9029</v>
       </c>
       <c r="N8" t="n">
         <v>276</v>
@@ -824,7 +824,7 @@
         <v>1.0591</v>
       </c>
       <c r="D9" t="n">
-        <v>0.694</v>
+        <v>0.6561</v>
       </c>
       <c r="E9" t="n">
         <v>2.761</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6872</v>
+        <v>1.6909</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6472</v>
+        <v>0.6486</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2602</v>
+        <v>0.2297</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6872</v>
+        <v>1.6909</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7669</v>
+        <v>1.7706</v>
       </c>
       <c r="G10" t="n">
         <v>-0.07969999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7669</v>
+        <v>1.7706</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4321</v>
+        <v>1.4351</v>
       </c>
       <c r="J10" t="n">
         <v>-0.07969999999999999</v>
@@ -897,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3524</v>
+        <v>1.3554</v>
       </c>
       <c r="N10" t="n">
         <v>184</v>
@@ -916,7 +916,7 @@
         <v>0.6425</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2552</v>
+        <v>0.2233</v>
       </c>
       <c r="E11" t="n">
         <v>1.6748</v>
@@ -962,7 +962,7 @@
         <v>0.6303</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2425</v>
+        <v>0.2107</v>
       </c>
       <c r="E12" t="n">
         <v>1.6432</v>
@@ -1008,7 +1008,7 @@
         <v>0.5569</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1651</v>
+        <v>0.1344</v>
       </c>
       <c r="E13" t="n">
         <v>1.4517</v>
@@ -1044,219 +1044,219 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1436</v>
+        <v>1.1845</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4387</v>
+        <v>0.4544</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0406</v>
+        <v>0.028</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1436</v>
+        <v>1.1845</v>
       </c>
       <c r="F14" t="n">
-        <v>0.889</v>
+        <v>1.2503</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2546</v>
+        <v>-0.0658</v>
       </c>
       <c r="H14" t="n">
-        <v>0.889</v>
+        <v>1.2503</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7206</v>
+        <v>1.0134</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2546</v>
+        <v>-0.0658</v>
       </c>
       <c r="K14" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="L14" t="n">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9752000000000001</v>
+        <v>0.9476000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>184</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.1525</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3633</v>
+        <v>0.4421</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0388</v>
+        <v>0.0152</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.1525</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.0736</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.0736</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.8702</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.0789</v>
       </c>
       <c r="K15" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9490999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8704</v>
+        <v>1.1436</v>
       </c>
       <c r="C16" t="n">
-        <v>0.3339</v>
+        <v>0.4387</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0697</v>
+        <v>0.0117</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8704</v>
+        <v>1.1436</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7915</v>
+        <v>0.889</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0789</v>
+        <v>0.2546</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7915</v>
+        <v>0.889</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6415</v>
+        <v>0.7206</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0789</v>
+        <v>0.2546</v>
       </c>
       <c r="K16" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7203999999999999</v>
+        <v>0.9752000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>135</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3018</v>
+        <v>0.3633</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1035</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8526</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0658</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8526</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6911</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0658</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="L17" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6253000000000001</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>276</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7387</v>
+        <v>0.8088</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2834</v>
+        <v>0.3103</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1229</v>
+        <v>-0.1217</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7387</v>
+        <v>0.8088</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4251</v>
+        <v>1.8088</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6864</v>
+        <v>-1</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4251</v>
+        <v>1.8088</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1551</v>
+        <v>1.4661</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6864</v>
+        <v>-1</v>
       </c>
       <c r="K18" t="n">
         <v>65</v>
@@ -1265,7 +1265,7 @@
         <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4687</v>
+        <v>0.4661</v>
       </c>
       <c r="N18" t="n">
         <v>135</v>
@@ -1274,35 +1274,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.65</v>
+        <v>0.7453</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2493</v>
+        <v>0.2859</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1588</v>
+        <v>-0.147</v>
       </c>
       <c r="E19" t="n">
-        <v>0.65</v>
+        <v>0.7453</v>
       </c>
       <c r="F19" t="n">
-        <v>1.65</v>
+        <v>1.4317</v>
       </c>
       <c r="G19" t="n">
-        <v>-1</v>
+        <v>-0.6864</v>
       </c>
       <c r="H19" t="n">
-        <v>1.65</v>
+        <v>1.4317</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3374</v>
+        <v>1.1604</v>
       </c>
       <c r="J19" t="n">
-        <v>-1</v>
+        <v>-0.6864</v>
       </c>
       <c r="K19" t="n">
         <v>65</v>
@@ -1311,7 +1311,7 @@
         <v>70</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3373999999999999</v>
+        <v>0.4740000000000001</v>
       </c>
       <c r="N19" t="n">
         <v>135</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.547</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2098</v>
+        <v>0.2496</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2004</v>
+        <v>-0.1847</v>
       </c>
       <c r="E20" t="n">
-        <v>0.547</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.547</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.547</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.547</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.547</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>103</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5023</v>
+        <v>0.6445</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1927</v>
+        <v>0.2472</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2184</v>
+        <v>-0.1871</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5023</v>
+        <v>0.6445</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5023</v>
+        <v>0.6445</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5023</v>
+        <v>0.6445</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5023</v>
+        <v>0.6445</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5023</v>
+        <v>0.6445</v>
       </c>
       <c r="N21" t="n">
         <v>103</v>
@@ -1412,216 +1412,216 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.434</v>
+        <v>0.606</v>
       </c>
       <c r="C22" t="n">
-        <v>0.1665</v>
+        <v>0.2325</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.246</v>
+        <v>-0.2025</v>
       </c>
       <c r="E22" t="n">
-        <v>0.434</v>
+        <v>0.606</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.606</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5306</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.606</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.606</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5306</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="L22" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4523</v>
+        <v>0.606</v>
       </c>
       <c r="N22" t="n">
-        <v>135</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3881</v>
+        <v>0.434</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1489</v>
+        <v>0.1665</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2646</v>
+        <v>-0.271</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3881</v>
+        <v>0.434</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3881</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.5306</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3881</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3881</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.5306</v>
       </c>
       <c r="K23" t="n">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3881</v>
+        <v>0.4523</v>
       </c>
       <c r="N23" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3131</v>
+        <v>0.3881</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1201</v>
+        <v>0.1489</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2949</v>
+        <v>-0.2893</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3131</v>
+        <v>0.3881</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3131</v>
+        <v>0.3881</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3131</v>
+        <v>0.3881</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3131</v>
+        <v>0.3881</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3131</v>
+        <v>0.3881</v>
       </c>
       <c r="N24" t="n">
-        <v>87</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.099</v>
+        <v>0.3618</v>
       </c>
       <c r="C25" t="n">
-        <v>0.038</v>
+        <v>0.1388</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3814</v>
+        <v>-0.2998</v>
       </c>
       <c r="E25" t="n">
-        <v>0.099</v>
+        <v>0.3618</v>
       </c>
       <c r="F25" t="n">
-        <v>0.099</v>
+        <v>0.3618</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.099</v>
+        <v>0.3618</v>
       </c>
       <c r="I25" t="n">
-        <v>0.099</v>
+        <v>0.3618</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.099</v>
+        <v>0.3618</v>
       </c>
       <c r="N25" t="n">
-        <v>152</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0254</v>
+        <v>0.038</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3946</v>
+        <v>-0.4045</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="I26" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.099</v>
       </c>
       <c r="N26" t="n">
         <v>152</v>
@@ -1642,93 +1642,93 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0604</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0232</v>
+        <v>0.0254</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4458</v>
+        <v>-0.4175</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0604</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0604</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0604</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0604</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0604</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0829</v>
+        <v>-0.0604</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0318</v>
+        <v>-0.0232</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4549</v>
+        <v>-0.468</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0829</v>
+        <v>-0.0604</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0829</v>
+        <v>-0.0604</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0829</v>
+        <v>-0.0604</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0829</v>
+        <v>-0.0604</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0829</v>
+        <v>-0.0604</v>
       </c>
       <c r="N28" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29">
@@ -1744,7 +1744,7 @@
         <v>-0.0948</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5212</v>
+        <v>-0.5424</v>
       </c>
       <c r="E29" t="n">
         <v>-0.2472</v>
@@ -1790,7 +1790,7 @@
         <v>-0.1132</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5405</v>
+        <v>-0.5614</v>
       </c>
       <c r="E30" t="n">
         <v>-0.295</v>
@@ -1836,7 +1836,7 @@
         <v>-0.1299</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5581</v>
+        <v>-0.5788</v>
       </c>
       <c r="E31" t="n">
         <v>-0.3386</v>
@@ -1882,7 +1882,7 @@
         <v>-0.1798</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6107</v>
+        <v>-0.6306</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4686</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1992</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6312</v>
+        <v>-0.6508</v>
       </c>
       <c r="E33" t="n">
         <v>-0.5194</v>
@@ -1964,139 +1964,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7826</v>
+        <v>-0.7713</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.3002</v>
+        <v>-0.2959</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7375</v>
+        <v>-0.7512</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7826</v>
+        <v>-0.7713</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7826</v>
+        <v>-0.7713</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7826</v>
+        <v>-0.7713</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7826</v>
+        <v>-0.7713</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7826</v>
+        <v>-0.7713</v>
       </c>
       <c r="N34" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8258</v>
+        <v>-0.7734</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.3168</v>
+        <v>-0.2967</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.755</v>
+        <v>-0.752</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8258</v>
+        <v>-0.7734</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8258</v>
+        <v>0.2266</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8258</v>
+        <v>0.2266</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8258</v>
+        <v>0.1837</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K35" t="n">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8258</v>
+        <v>-0.8163</v>
       </c>
       <c r="N35" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9136</v>
+        <v>-0.7826</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3505</v>
+        <v>-0.3002</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7904</v>
+        <v>-0.7557</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9136</v>
+        <v>-0.7826</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0864</v>
+        <v>-0.7826</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0864</v>
+        <v>-0.7826</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0701</v>
+        <v>-0.7826</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="L36" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.7826</v>
       </c>
       <c r="N36" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
@@ -2112,7 +2112,7 @@
         <v>-0.3884</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8303</v>
+        <v>-0.8473000000000001</v>
       </c>
       <c r="E37" t="n">
         <v>-1.0124</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3989</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8415</v>
+        <v>-0.8582</v>
       </c>
       <c r="E38" t="n">
         <v>-1.04</v>
@@ -2204,7 +2204,7 @@
         <v>-0.6686</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1255</v>
+        <v>-1.1383</v>
       </c>
       <c r="E39" t="n">
         <v>-1.743</v>
@@ -2250,7 +2250,7 @@
         <v>-0.6735</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1306</v>
+        <v>-1.1434</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7557</v>
@@ -2296,7 +2296,7 @@
         <v>-0.9338</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4048</v>
+        <v>-1.4138</v>
       </c>
       <c r="E41" t="n">
         <v>-2.4344</v>

--- a/database/event/2130/event_2130_evp_summary.xlsx
+++ b/database/event/2130/event_2130_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.2707</v>
+        <v>7.7043</v>
       </c>
       <c r="C2" t="n">
-        <v>3.1726</v>
+        <v>2.9554</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8511</v>
+        <v>2.8401</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2707</v>
+        <v>7.7043</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2001</v>
+        <v>3.043</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0706</v>
+        <v>4.6613</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2001</v>
+        <v>5.2355</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5938</v>
+        <v>2.7222</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0706</v>
+        <v>4.6613</v>
       </c>
       <c r="K2" t="n">
         <v>167</v>
@@ -529,7 +529,7 @@
         <v>213</v>
       </c>
       <c r="M2" t="n">
-        <v>7.6644</v>
+        <v>7.3835</v>
       </c>
       <c r="N2" t="n">
         <v>380</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6823</v>
+        <v>6.6441</v>
       </c>
       <c r="C3" t="n">
-        <v>2.9469</v>
+        <v>2.5487</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6167</v>
+        <v>2.3615</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6823</v>
+        <v>6.6441</v>
       </c>
       <c r="F3" t="n">
-        <v>4.3076</v>
+        <v>3.7035</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3747</v>
+        <v>2.9406</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7701</v>
+        <v>7.5624</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8663</v>
+        <v>3.9321</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3747</v>
+        <v>2.9406</v>
       </c>
       <c r="K3" t="n">
         <v>167</v>
@@ -575,7 +575,7 @@
         <v>213</v>
       </c>
       <c r="M3" t="n">
-        <v>7.241</v>
+        <v>6.8727</v>
       </c>
       <c r="N3" t="n">
         <v>380</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0876</v>
+        <v>6.2738</v>
       </c>
       <c r="C4" t="n">
-        <v>2.3352</v>
+        <v>2.4066</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9814</v>
+        <v>2.1943</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0876</v>
+        <v>6.2738</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8205</v>
+        <v>2.414</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2671</v>
+        <v>3.8598</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8205</v>
+        <v>3.0191</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4756</v>
+        <v>1.5698</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2671</v>
+        <v>3.8598</v>
       </c>
       <c r="K4" t="n">
         <v>51</v>
@@ -621,7 +621,7 @@
         <v>225</v>
       </c>
       <c r="M4" t="n">
-        <v>5.7427</v>
+        <v>5.4296</v>
       </c>
       <c r="N4" t="n">
         <v>276</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.1082</v>
+        <v>5.4526</v>
       </c>
       <c r="C5" t="n">
-        <v>1.9595</v>
+        <v>2.0916</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5912</v>
+        <v>1.8236</v>
       </c>
       <c r="E5" t="n">
-        <v>5.1082</v>
+        <v>5.4526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.269</v>
+        <v>0.9649</v>
       </c>
       <c r="G5" t="n">
-        <v>4.8392</v>
+        <v>4.4877</v>
       </c>
       <c r="H5" t="n">
-        <v>0.269</v>
+        <v>0.9649</v>
       </c>
       <c r="I5" t="n">
-        <v>0.218</v>
+        <v>0.5017</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8392</v>
+        <v>4.4877</v>
       </c>
       <c r="K5" t="n">
         <v>167</v>
@@ -667,7 +667,7 @@
         <v>213</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0572</v>
+        <v>4.9894</v>
       </c>
       <c r="N5" t="n">
         <v>380</v>
@@ -676,185 +676,185 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>ScreaM</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0908</v>
+        <v>4.5007</v>
       </c>
       <c r="C6" t="n">
-        <v>1.5692</v>
+        <v>1.7265</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1859</v>
+        <v>1.3938</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0908</v>
+        <v>4.5007</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7476</v>
+        <v>1.8748</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3432</v>
+        <v>2.6259</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7476</v>
+        <v>1.8748</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0375</v>
+        <v>0.9748</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3432</v>
+        <v>2.6259</v>
       </c>
       <c r="K6" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="L6" t="n">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3807</v>
+        <v>3.6007</v>
       </c>
       <c r="N6" t="n">
-        <v>184</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ScreaM</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7734</v>
+        <v>3.5888</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4475</v>
+        <v>1.3767</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0594</v>
+        <v>0.9822</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7734</v>
+        <v>3.5888</v>
       </c>
       <c r="F7" t="n">
-        <v>1.141</v>
+        <v>2.176</v>
       </c>
       <c r="G7" t="n">
-        <v>2.6324</v>
+        <v>1.4128</v>
       </c>
       <c r="H7" t="n">
-        <v>1.141</v>
+        <v>2.1804</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9248</v>
+        <v>1.1337</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6324</v>
+        <v>1.4128</v>
       </c>
       <c r="K7" t="n">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="L7" t="n">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5572</v>
+        <v>2.5465</v>
       </c>
       <c r="N7" t="n">
-        <v>276</v>
+        <v>380</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.3749</v>
+        <v>3.5685</v>
       </c>
       <c r="C8" t="n">
-        <v>1.2946</v>
+        <v>1.3689</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9006999999999999</v>
+        <v>0.973</v>
       </c>
       <c r="E8" t="n">
-        <v>3.3749</v>
+        <v>3.5685</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4913</v>
+        <v>3.3279</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.2406</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4913</v>
+        <v>6.2392</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0193</v>
+        <v>3.2441</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.2406</v>
       </c>
       <c r="K8" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="L8" t="n">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9029</v>
+        <v>3.4847</v>
       </c>
       <c r="N8" t="n">
-        <v>276</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.761</v>
+        <v>3.534</v>
       </c>
       <c r="C9" t="n">
-        <v>1.0591</v>
+        <v>1.3556</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6561</v>
+        <v>0.9574</v>
       </c>
       <c r="E9" t="n">
-        <v>2.761</v>
+        <v>3.534</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9493</v>
+        <v>2.6687</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8118</v>
+        <v>0.8653</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9493</v>
+        <v>3.9165</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7694</v>
+        <v>2.0364</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8118</v>
+        <v>0.8653</v>
       </c>
       <c r="K9" t="n">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5812</v>
+        <v>2.9017</v>
       </c>
       <c r="N9" t="n">
-        <v>380</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.6909</v>
+        <v>2.4904</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6486</v>
+        <v>0.9553</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2297</v>
+        <v>0.4863</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6909</v>
+        <v>2.4904</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7706</v>
+        <v>2.4555</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0349</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7706</v>
+        <v>3.1653</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4351</v>
+        <v>1.6458</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0.0349</v>
       </c>
       <c r="K10" t="n">
         <v>102</v>
@@ -897,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3554</v>
+        <v>1.6807</v>
       </c>
       <c r="N10" t="n">
         <v>184</v>
@@ -906,47 +906,47 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.6748</v>
+        <v>2.2813</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6425</v>
+        <v>0.8751</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2233</v>
+        <v>0.3919</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6748</v>
+        <v>2.2813</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6748</v>
+        <v>1.8492</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.4321</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6748</v>
+        <v>1.8492</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6748</v>
+        <v>0.9615</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.4321</v>
       </c>
       <c r="K11" t="n">
-        <v>152</v>
+        <v>51</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="M11" t="n">
-        <v>1.6748</v>
+        <v>1.3936</v>
       </c>
       <c r="N11" t="n">
-        <v>152</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.6432</v>
+        <v>2.0113</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6303</v>
+        <v>0.7715</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2107</v>
+        <v>0.27</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6432</v>
+        <v>2.0113</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6432</v>
+        <v>2.0113</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6432</v>
+        <v>2.0113</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6432</v>
+        <v>2.0113</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6432</v>
+        <v>2.0113</v>
       </c>
       <c r="N12" t="n">
         <v>105</v>
@@ -998,32 +998,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.4517</v>
+        <v>1.9478</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5569</v>
+        <v>0.7472</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1344</v>
+        <v>0.2413</v>
       </c>
       <c r="E13" t="n">
-        <v>1.4517</v>
+        <v>1.9478</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4517</v>
+        <v>1.9478</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4517</v>
+        <v>1.9478</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4517</v>
+        <v>1.9478</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4517</v>
+        <v>1.9478</v>
       </c>
       <c r="N13" t="n">
         <v>152</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.1845</v>
+        <v>1.8041</v>
       </c>
       <c r="C14" t="n">
-        <v>0.4544</v>
+        <v>0.6921</v>
       </c>
       <c r="D14" t="n">
-        <v>0.028</v>
+        <v>0.1764</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1845</v>
+        <v>1.8041</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2503</v>
+        <v>2.2104</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0658</v>
+        <v>-0.4063</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2503</v>
+        <v>2.3017</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0134</v>
+        <v>1.1968</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0658</v>
+        <v>-0.4063</v>
       </c>
       <c r="K14" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="L14" t="n">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9476000000000001</v>
+        <v>0.7905000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>276</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1525</v>
+        <v>1.7716</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4421</v>
+        <v>0.6796</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0152</v>
+        <v>0.1618</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1525</v>
+        <v>1.7716</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0736</v>
+        <v>1.5582</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0789</v>
+        <v>0.2134</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0736</v>
+        <v>1.5582</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8702</v>
+        <v>0.8102</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0789</v>
+        <v>0.2134</v>
       </c>
       <c r="K15" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="L15" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9490999999999999</v>
+        <v>1.0236</v>
       </c>
       <c r="N15" t="n">
-        <v>135</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1436</v>
+        <v>1.7461</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4387</v>
+        <v>0.6698</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0117</v>
+        <v>0.1503</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1436</v>
+        <v>1.7461</v>
       </c>
       <c r="F16" t="n">
-        <v>0.889</v>
+        <v>1.6738</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2546</v>
+        <v>0.0723</v>
       </c>
       <c r="H16" t="n">
-        <v>0.889</v>
+        <v>1.6738</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7206</v>
+        <v>0.8703</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2546</v>
+        <v>0.0723</v>
       </c>
       <c r="K16" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="L16" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9752000000000001</v>
+        <v>0.9426</v>
       </c>
       <c r="N16" t="n">
-        <v>184</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.7089</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3633</v>
+        <v>0.6555</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.1335</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.7089</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.7089</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.7089</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.7089</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.7089</v>
       </c>
       <c r="N17" t="n">
-        <v>87</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8088</v>
+        <v>1.5669</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3103</v>
+        <v>0.6011</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1217</v>
+        <v>0.0694</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8088</v>
+        <v>1.5669</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8088</v>
+        <v>2.3821</v>
       </c>
       <c r="G18" t="n">
-        <v>-1</v>
+        <v>-0.8152</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8088</v>
+        <v>2.9066</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4661</v>
+        <v>1.5113</v>
       </c>
       <c r="J18" t="n">
-        <v>-1</v>
+        <v>-0.8152</v>
       </c>
       <c r="K18" t="n">
         <v>65</v>
@@ -1265,7 +1265,7 @@
         <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4661</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>135</v>
@@ -1274,47 +1274,47 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7453</v>
+        <v>1.0509</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2859</v>
+        <v>0.4031</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.147</v>
+        <v>-0.1636</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7453</v>
+        <v>1.0509</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4317</v>
+        <v>1.0509</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6864</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4317</v>
+        <v>1.0509</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1604</v>
+        <v>1.0509</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6864</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="L19" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4740000000000001</v>
+        <v>1.0509</v>
       </c>
       <c r="N19" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6506999999999999</v>
+        <v>1.0082</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2496</v>
+        <v>0.3867</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1847</v>
+        <v>-0.1829</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6506999999999999</v>
+        <v>1.0082</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6506999999999999</v>
+        <v>1.0082</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6506999999999999</v>
+        <v>1.0082</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6506999999999999</v>
+        <v>1.0082</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6506999999999999</v>
+        <v>1.0082</v>
       </c>
       <c r="N20" t="n">
         <v>103</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6445</v>
+        <v>0.953</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2472</v>
+        <v>0.3656</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1871</v>
+        <v>-0.2078</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6445</v>
+        <v>0.953</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6445</v>
+        <v>0.953</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6445</v>
+        <v>0.953</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6445</v>
+        <v>0.953</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6445</v>
+        <v>0.953</v>
       </c>
       <c r="N21" t="n">
         <v>103</v>
@@ -1412,139 +1412,139 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>wenton</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.606</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2325</v>
+        <v>0.3177</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2025</v>
+        <v>-0.2642</v>
       </c>
       <c r="E22" t="n">
-        <v>0.606</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.606</v>
+        <v>1.032</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.2039</v>
       </c>
       <c r="H22" t="n">
-        <v>0.606</v>
+        <v>1.032</v>
       </c>
       <c r="I22" t="n">
-        <v>0.606</v>
+        <v>0.5366</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.2039</v>
       </c>
       <c r="K22" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M22" t="n">
-        <v>0.606</v>
+        <v>0.3327</v>
       </c>
       <c r="N22" t="n">
-        <v>103</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.434</v>
+        <v>0.7332</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1665</v>
+        <v>0.2813</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.271</v>
+        <v>-0.307</v>
       </c>
       <c r="E23" t="n">
-        <v>0.434</v>
+        <v>0.7332</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.7332</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5306</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.7332</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.7332</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5306</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="L23" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4523</v>
+        <v>0.7332</v>
       </c>
       <c r="N23" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3881</v>
+        <v>0.7218</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1489</v>
+        <v>0.2769</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2893</v>
+        <v>-0.3122</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3881</v>
+        <v>0.7218</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3881</v>
+        <v>0.7218</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3881</v>
+        <v>0.7218</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3881</v>
+        <v>0.7218</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3881</v>
+        <v>0.7218</v>
       </c>
       <c r="N24" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3618</v>
+        <v>0.6694</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1388</v>
+        <v>0.2568</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.2998</v>
+        <v>-0.3358</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3618</v>
+        <v>0.6694</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3618</v>
+        <v>0.6694</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3618</v>
+        <v>0.6694</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3618</v>
+        <v>0.6694</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3618</v>
+        <v>0.6694</v>
       </c>
       <c r="N25" t="n">
         <v>87</v>
@@ -1596,277 +1596,277 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.099</v>
+        <v>0.6473</v>
       </c>
       <c r="C26" t="n">
-        <v>0.038</v>
+        <v>0.2483</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4045</v>
+        <v>-0.3458</v>
       </c>
       <c r="E26" t="n">
-        <v>0.099</v>
+        <v>0.6473</v>
       </c>
       <c r="F26" t="n">
-        <v>0.099</v>
+        <v>1.0822</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-0.4349</v>
       </c>
       <c r="H26" t="n">
-        <v>0.099</v>
+        <v>1.0822</v>
       </c>
       <c r="I26" t="n">
-        <v>0.099</v>
+        <v>0.5627</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-0.4349</v>
       </c>
       <c r="K26" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M26" t="n">
-        <v>0.099</v>
+        <v>0.1278</v>
       </c>
       <c r="N26" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.5614</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0254</v>
+        <v>0.2154</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4175</v>
+        <v>-0.3846</v>
       </c>
       <c r="E27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.5614</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0515</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.5099</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0515</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0268</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>0.5099</v>
       </c>
       <c r="K27" t="n">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.5367000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0604</v>
+        <v>0.4133</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0232</v>
+        <v>0.1585</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.468</v>
+        <v>-0.4514</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0604</v>
+        <v>0.4133</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0604</v>
+        <v>0.4133</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0604</v>
+        <v>0.4133</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0604</v>
+        <v>0.4133</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0604</v>
+        <v>0.4133</v>
       </c>
       <c r="N28" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2472</v>
+        <v>0.3446</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0948</v>
+        <v>0.1322</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5424</v>
+        <v>-0.4824</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2472</v>
+        <v>0.3446</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.2472</v>
+        <v>0.3446</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2472</v>
+        <v>0.3446</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2472</v>
+        <v>0.3446</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2472</v>
+        <v>0.3446</v>
       </c>
       <c r="N29" t="n">
-        <v>105</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>wenton</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.295</v>
+        <v>0.1942</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1132</v>
+        <v>0.0745</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5614</v>
+        <v>-0.5503</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.295</v>
+        <v>0.1942</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2533</v>
+        <v>1.1972</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.5483</v>
+        <v>-1.003</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2533</v>
+        <v>1.1972</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2053</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.5483</v>
+        <v>-1.003</v>
       </c>
       <c r="K30" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="L30" t="n">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.343</v>
+        <v>-0.3804999999999998</v>
       </c>
       <c r="N30" t="n">
-        <v>184</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3386</v>
+        <v>0.1936</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.1299</v>
+        <v>0.0743</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5788</v>
+        <v>-0.5506</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3386</v>
+        <v>0.1936</v>
       </c>
       <c r="F31" t="n">
-        <v>0.339</v>
+        <v>0.1936</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.6776</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.339</v>
+        <v>0.1936</v>
       </c>
       <c r="I31" t="n">
-        <v>0.2748</v>
+        <v>0.1936</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.6776</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="L31" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4028</v>
+        <v>0.1936</v>
       </c>
       <c r="N31" t="n">
-        <v>184</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4686</v>
+        <v>-0.0246</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1798</v>
+        <v>-0.0094</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6306</v>
+        <v>-0.6491</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4686</v>
+        <v>-0.0246</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4686</v>
+        <v>-0.0246</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4686</v>
+        <v>-0.0246</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4686</v>
+        <v>-0.0246</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4686</v>
+        <v>-0.0246</v>
       </c>
       <c r="N32" t="n">
         <v>105</v>
@@ -1918,47 +1918,47 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5194</v>
+        <v>-0.0491</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1992</v>
+        <v>-0.0188</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6508</v>
+        <v>-0.6602</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5194</v>
+        <v>-0.0491</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5194</v>
+        <v>-0.0491</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5194</v>
+        <v>-0.0491</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5194</v>
+        <v>-0.0491</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5194</v>
+        <v>-0.0491</v>
       </c>
       <c r="N33" t="n">
-        <v>87</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7713</v>
+        <v>-0.236</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.2959</v>
+        <v>-0.0905</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7512</v>
+        <v>-0.7446</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7713</v>
+        <v>-0.236</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7713</v>
+        <v>-0.236</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7713</v>
+        <v>-0.236</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7713</v>
+        <v>-0.236</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7713</v>
+        <v>-0.236</v>
       </c>
       <c r="N34" t="n">
         <v>103</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7734</v>
+        <v>-0.3465</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.2967</v>
+        <v>-0.1329</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.752</v>
+        <v>-0.7944</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7734</v>
+        <v>-0.3465</v>
       </c>
       <c r="F35" t="n">
-        <v>0.2266</v>
+        <v>0.4689</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>-0.8154</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2266</v>
+        <v>0.4689</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1837</v>
+        <v>0.2438</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>-0.8154</v>
       </c>
       <c r="K35" t="n">
         <v>65</v>
@@ -2047,7 +2047,7 @@
         <v>70</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8163</v>
+        <v>-0.5716</v>
       </c>
       <c r="N35" t="n">
         <v>135</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7826</v>
+        <v>-0.3635</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.3002</v>
+        <v>-0.1394</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.7557</v>
+        <v>-0.8021</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7826</v>
+        <v>-0.3635</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7826</v>
+        <v>-0.3635</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7826</v>
+        <v>-0.3635</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7826</v>
+        <v>-0.3635</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7826</v>
+        <v>-0.3635</v>
       </c>
       <c r="N36" t="n">
         <v>87</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0124</v>
+        <v>-0.4932</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.3884</v>
+        <v>-0.1892</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8473000000000001</v>
+        <v>-0.8607</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0124</v>
+        <v>-0.4932</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.4932</v>
       </c>
       <c r="G37" t="n">
-        <v>-1.5935</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.4932</v>
       </c>
       <c r="I37" t="n">
-        <v>0.471</v>
+        <v>-0.4932</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.5935</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="L37" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.1225</v>
+        <v>-0.4932</v>
       </c>
       <c r="N37" t="n">
-        <v>276</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.04</v>
+        <v>-0.592</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3989</v>
+        <v>-0.2271</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8582</v>
+        <v>-0.9053</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.04</v>
+        <v>-0.592</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.04</v>
+        <v>-0.592</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.04</v>
+        <v>-0.592</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.04</v>
+        <v>-0.592</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.04</v>
+        <v>-0.592</v>
       </c>
       <c r="N38" t="n">
         <v>105</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>Slemmy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.743</v>
+        <v>-1.1704</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.6686</v>
+        <v>-0.449</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1383</v>
+        <v>-1.1664</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.743</v>
+        <v>-1.1704</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.743</v>
+        <v>-1.1704</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.743</v>
+        <v>-1.1704</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.743</v>
+        <v>-1.1704</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.743</v>
+        <v>-1.1704</v>
       </c>
       <c r="N39" t="n">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Slemmy</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7557</v>
+        <v>-1.3476</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6735</v>
+        <v>-0.5169</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1434</v>
+        <v>-1.2464</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7557</v>
+        <v>-1.3476</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.7557</v>
+        <v>-1.3476</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.7557</v>
+        <v>-1.3476</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.7557</v>
+        <v>-1.3476</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7557</v>
+        <v>-1.3476</v>
       </c>
       <c r="N40" t="n">
-        <v>87</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.4344</v>
+        <v>-1.9315</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.9338</v>
+        <v>-0.7409</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4138</v>
+        <v>-1.51</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.4344</v>
+        <v>-1.9315</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4417</v>
+        <v>-1.2892</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.9927</v>
+        <v>-0.6423</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4417</v>
+        <v>-1.2892</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1685</v>
+        <v>-0.6703</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9927</v>
+        <v>-0.6423</v>
       </c>
       <c r="K41" t="n">
         <v>167</v>
@@ -2323,7 +2323,7 @@
         <v>213</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.1612</v>
+        <v>-1.3126</v>
       </c>
       <c r="N41" t="n">
         <v>380</v>
@@ -2429,10 +2429,10 @@
         <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4517</v>
+        <v>0.4007</v>
       </c>
       <c r="J2" t="n">
-        <v>11.7442</v>
+        <v>10.4182</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2409</v>
+        <v>0.1955</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2634</v>
+        <v>5.083</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0404</v>
+        <v>-0.0337</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.0504</v>
+        <v>-0.8762</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3898</v>
+        <v>-0.245</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.1348</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4872</v>
+        <v>-0.3132</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.6672</v>
+        <v>-8.1432</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9201</v>
+        <v>0.8363</v>
       </c>
       <c r="J7" t="n">
-        <v>23.9226</v>
+        <v>21.7438</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2703</v>
+        <v>0.2477</v>
       </c>
       <c r="J8" t="n">
-        <v>7.0278</v>
+        <v>6.4402</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.07</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0931</v>
+        <v>0.112</v>
       </c>
       <c r="J9" t="n">
-        <v>2.4206</v>
+        <v>2.912</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0299</v>
+        <v>0.0072</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7774</v>
+        <v>0.1872</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.268</v>
+        <v>-0.1521</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.968</v>
+        <v>-3.9546</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4947</v>
+        <v>1.3184</v>
       </c>
       <c r="J12" t="n">
-        <v>43.3463</v>
+        <v>38.2336</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8844</v>
+        <v>0.8759</v>
       </c>
       <c r="J13" t="n">
-        <v>25.6476</v>
+        <v>25.4011</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1025</v>
+        <v>0.1627</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9725</v>
+        <v>4.7183</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.89</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4907</v>
+        <v>-0.4215</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.2303</v>
+        <v>-12.2235</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4907</v>
+        <v>-0.4215</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.2303</v>
+        <v>-12.2235</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7478</v>
+        <v>0.9308</v>
       </c>
       <c r="J17" t="n">
-        <v>21.6862</v>
+        <v>26.9932</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0291</v>
+        <v>-0.0318</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8439</v>
+        <v>-0.9222</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3549</v>
+        <v>-0.2225</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.2921</v>
+        <v>-6.4525</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4416</v>
+        <v>-0.2819</v>
       </c>
       <c r="J20" t="n">
-        <v>-12.8064</v>
+        <v>-8.1751</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4829</v>
+        <v>-0.3108</v>
       </c>
       <c r="J21" t="n">
-        <v>-14.0041</v>
+        <v>-9.013199999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.99</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0535</v>
+        <v>0.0076</v>
       </c>
       <c r="J22" t="n">
-        <v>1.391</v>
+        <v>0.1976</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.92</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0925</v>
+        <v>-0.0907</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.405</v>
+        <v>-2.3582</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2739</v>
+        <v>-0.198</v>
       </c>
       <c r="J24" t="n">
-        <v>-7.1214</v>
+        <v>-5.148</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4313</v>
+        <v>-0.2842</v>
       </c>
       <c r="J25" t="n">
-        <v>-11.2138</v>
+        <v>-7.3892</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5854</v>
+        <v>-0.3883</v>
       </c>
       <c r="J26" t="n">
-        <v>-15.2204</v>
+        <v>-10.0958</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.65</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8349</v>
+        <v>0.7575</v>
       </c>
       <c r="J27" t="n">
-        <v>21.7074</v>
+        <v>19.695</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4629</v>
+        <v>0.4301</v>
       </c>
       <c r="J28" t="n">
-        <v>12.0354</v>
+        <v>11.1826</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.28</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3681</v>
+        <v>0.3645</v>
       </c>
       <c r="J29" t="n">
-        <v>9.570600000000001</v>
+        <v>9.477</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.27</v>
       </c>
       <c r="I30" t="n">
-        <v>0.354</v>
+        <v>0.3531</v>
       </c>
       <c r="J30" t="n">
-        <v>9.204000000000001</v>
+        <v>9.1806</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.09</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0907</v>
+        <v>0.1229</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3582</v>
+        <v>3.1954</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.89</v>
       </c>
       <c r="I32" t="n">
-        <v>1.9275</v>
+        <v>1.6238</v>
       </c>
       <c r="J32" t="n">
-        <v>52.0425</v>
+        <v>43.8426</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.39</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9941</v>
+        <v>0.9879</v>
       </c>
       <c r="J33" t="n">
-        <v>26.8407</v>
+        <v>26.6733</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.36</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9286</v>
+        <v>0.929</v>
       </c>
       <c r="J34" t="n">
-        <v>25.0722</v>
+        <v>25.083</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5824</v>
+        <v>-0.5159</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.7248</v>
+        <v>-13.9293</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.5</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3608</v>
+        <v>-1.3898</v>
       </c>
       <c r="J36" t="n">
-        <v>-36.7416</v>
+        <v>-37.5246</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.24</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4602</v>
+        <v>0.5333</v>
       </c>
       <c r="J37" t="n">
-        <v>12.4254</v>
+        <v>14.3991</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.92</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1682</v>
+        <v>-0.1058</v>
       </c>
       <c r="J38" t="n">
-        <v>-4.5414</v>
+        <v>-2.8566</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.89</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2242</v>
+        <v>-0.1388</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.0534</v>
+        <v>-3.7476</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2417</v>
+        <v>-0.1496</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.5259</v>
+        <v>-4.0392</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.398</v>
+        <v>-0.252</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.746</v>
+        <v>-6.804</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.44</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0787</v>
+        <v>1.0548</v>
       </c>
       <c r="J42" t="n">
-        <v>37.7545</v>
+        <v>36.918</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.41</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0152</v>
+        <v>1.0112</v>
       </c>
       <c r="J43" t="n">
-        <v>35.532</v>
+        <v>35.392</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.34</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8606</v>
+        <v>0.8729</v>
       </c>
       <c r="J44" t="n">
-        <v>30.121</v>
+        <v>30.5515</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0339</v>
+        <v>0.1089</v>
       </c>
       <c r="J45" t="n">
-        <v>1.1865</v>
+        <v>3.8115</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.98</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2377</v>
+        <v>-0.1551</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.3195</v>
+        <v>-5.4285</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4543</v>
+        <v>0.5244</v>
       </c>
       <c r="J47" t="n">
-        <v>15.9005</v>
+        <v>18.354</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.11</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2749</v>
+        <v>0.2909</v>
       </c>
       <c r="J48" t="n">
-        <v>9.621499999999999</v>
+        <v>10.1815</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.85</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2837</v>
+        <v>-0.1786</v>
       </c>
       <c r="J49" t="n">
-        <v>-9.929500000000001</v>
+        <v>-6.251</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.347</v>
+        <v>-0.2193</v>
       </c>
       <c r="J50" t="n">
-        <v>-12.145</v>
+        <v>-7.6755</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6331</v>
+        <v>-0.4204</v>
       </c>
       <c r="J51" t="n">
-        <v>-22.1585</v>
+        <v>-14.714</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2957</v>
+        <v>0.2417</v>
       </c>
       <c r="J52" t="n">
-        <v>8.871</v>
+        <v>7.251</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.99</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0145</v>
+        <v>-0.0112</v>
       </c>
       <c r="J53" t="n">
-        <v>0.435</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0111</v>
+        <v>-0.0272</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.333</v>
+        <v>-0.8159999999999999</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3431</v>
+        <v>-0.2179</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.293</v>
+        <v>-6.537</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5802</v>
+        <v>-0.3818</v>
       </c>
       <c r="J56" t="n">
-        <v>-17.406</v>
+        <v>-11.454</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.92</v>
       </c>
       <c r="I57" t="n">
-        <v>1.1543</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>34.629</v>
+        <v>23.181</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.12</v>
       </c>
       <c r="I58" t="n">
-        <v>0.181</v>
+        <v>0.1839</v>
       </c>
       <c r="J58" t="n">
-        <v>5.43</v>
+        <v>5.517</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.01</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.029</v>
+        <v>0.0078</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.87</v>
+        <v>0.234</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2673</v>
+        <v>-0.1517</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.019</v>
+        <v>-4.551</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3138</v>
+        <v>-0.1845</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.414</v>
+        <v>-5.535</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.78</v>
       </c>
       <c r="I62" t="n">
-        <v>1.6783</v>
+        <v>1.1755</v>
       </c>
       <c r="J62" t="n">
-        <v>40.2792</v>
+        <v>28.212</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>1.3509</v>
+        <v>0.9609</v>
       </c>
       <c r="J63" t="n">
-        <v>32.4216</v>
+        <v>23.0616</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I64" t="n">
-        <v>0.916</v>
+        <v>0.7023</v>
       </c>
       <c r="J64" t="n">
-        <v>21.984</v>
+        <v>16.8552</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.15</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3129</v>
+        <v>0.3762</v>
       </c>
       <c r="J65" t="n">
-        <v>7.5096</v>
+        <v>9.0288</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.783</v>
+        <v>-0.7315</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.792</v>
+        <v>-17.556</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2267</v>
+        <v>0.2202</v>
       </c>
       <c r="J67" t="n">
-        <v>5.4408</v>
+        <v>5.2848</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0856</v>
+        <v>0.0475</v>
       </c>
       <c r="J68" t="n">
-        <v>2.0544</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.86</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2027</v>
+        <v>-0.1586</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.8648</v>
+        <v>-3.8064</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.5869</v>
+        <v>-0.3891</v>
       </c>
       <c r="J70" t="n">
-        <v>-14.0856</v>
+        <v>-9.3384</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.6516</v>
+        <v>-0.4357</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.6384</v>
+        <v>-10.4568</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.6947</v>
       </c>
       <c r="J72" t="n">
-        <v>26.6868</v>
+        <v>19.4516</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5437</v>
+        <v>0.4577</v>
       </c>
       <c r="J73" t="n">
-        <v>15.2236</v>
+        <v>12.8156</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.4432</v>
       </c>
       <c r="J74" t="n">
-        <v>14.4368</v>
+        <v>12.4096</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2006</v>
+        <v>0.2558</v>
       </c>
       <c r="J75" t="n">
-        <v>5.6168</v>
+        <v>7.1624</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.96</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2791</v>
+        <v>-0.2052</v>
       </c>
       <c r="J76" t="n">
-        <v>-7.8148</v>
+        <v>-5.7456</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3524</v>
+        <v>0.3697</v>
       </c>
       <c r="J77" t="n">
-        <v>9.8672</v>
+        <v>10.3516</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.012</v>
+        <v>-0.018</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.336</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0391</v>
+        <v>-0.0336</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.0948</v>
+        <v>-0.9408</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1595</v>
+        <v>-0.0964</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.466</v>
+        <v>-2.6992</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4459</v>
+        <v>-0.2841</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.4852</v>
+        <v>-7.9548</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.93</v>
       </c>
       <c r="I82" t="n">
-        <v>0.0123</v>
+        <v>-0.0265</v>
       </c>
       <c r="J82" t="n">
-        <v>0.246</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0237</v>
+        <v>-0.0527</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.474</v>
+        <v>-1.054</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.62</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.5097</v>
+        <v>-0.3604</v>
       </c>
       <c r="J84" t="n">
-        <v>-10.194</v>
+        <v>-7.208</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.7323</v>
+        <v>-0.4996</v>
       </c>
       <c r="J85" t="n">
-        <v>-14.646</v>
+        <v>-9.992000000000001</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.24</v>
       </c>
       <c r="I86" t="n">
-        <v>-1.0178</v>
+        <v>-0.7181</v>
       </c>
       <c r="J86" t="n">
-        <v>-20.356</v>
+        <v>-14.362</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.95</v>
       </c>
       <c r="I87" t="n">
-        <v>1.816</v>
+        <v>1.3248</v>
       </c>
       <c r="J87" t="n">
-        <v>36.32</v>
+        <v>26.496</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.79</v>
       </c>
       <c r="I88" t="n">
-        <v>1.6159</v>
+        <v>1.1465</v>
       </c>
       <c r="J88" t="n">
-        <v>32.318</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.48</v>
       </c>
       <c r="I89" t="n">
-        <v>0.9795</v>
+        <v>0.7935</v>
       </c>
       <c r="J89" t="n">
-        <v>19.59</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.32</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6414</v>
+        <v>0.5924</v>
       </c>
       <c r="J90" t="n">
-        <v>12.828</v>
+        <v>11.848</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.18</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3281</v>
+        <v>0.3968</v>
       </c>
       <c r="J91" t="n">
-        <v>6.562</v>
+        <v>7.936</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5472</v>
+        <v>0.4174</v>
       </c>
       <c r="J92" t="n">
-        <v>13.1328</v>
+        <v>10.0176</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.26</v>
       </c>
       <c r="I93" t="n">
-        <v>0.4151</v>
+        <v>0.348</v>
       </c>
       <c r="J93" t="n">
-        <v>9.962400000000001</v>
+        <v>8.352</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1669</v>
+        <v>0.1711</v>
       </c>
       <c r="J94" t="n">
-        <v>4.0056</v>
+        <v>4.1064</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.1</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1497</v>
+        <v>0.1572</v>
       </c>
       <c r="J95" t="n">
-        <v>3.5928</v>
+        <v>3.7728</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.18</v>
+        <v>-0.092</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.32</v>
+        <v>-2.208</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.25</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4832</v>
+        <v>0.3911</v>
       </c>
       <c r="J97" t="n">
-        <v>11.5968</v>
+        <v>9.3864</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1026</v>
+        <v>-0.081</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.4624</v>
+        <v>-1.944</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.172</v>
+        <v>-0.1147</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.128</v>
+        <v>-2.7528</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3457</v>
+        <v>-0.2189</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.296799999999999</v>
+        <v>-5.2536</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5429</v>
+        <v>-0.3546</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.0296</v>
+        <v>-8.510400000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4046</v>
+        <v>0.4054</v>
       </c>
       <c r="J102" t="n">
-        <v>10.5196</v>
+        <v>10.5404</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.98</v>
       </c>
       <c r="I103" t="n">
-        <v>0.0396</v>
+        <v>-0.0051</v>
       </c>
       <c r="J103" t="n">
-        <v>1.0296</v>
+        <v>-0.1326</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4806</v>
+        <v>-0.3186</v>
       </c>
       <c r="J104" t="n">
-        <v>-12.4956</v>
+        <v>-8.2836</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5918</v>
+        <v>-0.3939</v>
       </c>
       <c r="J105" t="n">
-        <v>-15.3868</v>
+        <v>-10.2414</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.4869</v>
       </c>
       <c r="J106" t="n">
-        <v>-18.7278</v>
+        <v>-12.6594</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.6</v>
       </c>
       <c r="I107" t="n">
-        <v>1.3328</v>
+        <v>0.9535</v>
       </c>
       <c r="J107" t="n">
-        <v>34.6528</v>
+        <v>24.791</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>1.027</v>
+        <v>0.7718</v>
       </c>
       <c r="J108" t="n">
-        <v>26.702</v>
+        <v>20.0668</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.9362</v>
+        <v>0.7229</v>
       </c>
       <c r="J109" t="n">
-        <v>24.3412</v>
+        <v>18.7954</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.33</v>
       </c>
       <c r="I110" t="n">
-        <v>0.7286</v>
+        <v>0.6239</v>
       </c>
       <c r="J110" t="n">
-        <v>18.9436</v>
+        <v>16.2214</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.12</v>
       </c>
       <c r="I111" t="n">
-        <v>0.2221</v>
+        <v>0.3155</v>
       </c>
       <c r="J111" t="n">
-        <v>5.7746</v>
+        <v>8.202999999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.88</v>
       </c>
       <c r="I112" t="n">
-        <v>1.84</v>
+        <v>1.5567</v>
       </c>
       <c r="J112" t="n">
-        <v>40.48</v>
+        <v>34.2474</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8299</v>
+        <v>0.9118000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>18.2578</v>
+        <v>20.0596</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.28</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6136</v>
+        <v>0.7149</v>
       </c>
       <c r="J114" t="n">
-        <v>13.4992</v>
+        <v>15.7278</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.4242</v>
+        <v>0.5248</v>
       </c>
       <c r="J115" t="n">
-        <v>9.3324</v>
+        <v>11.5456</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.16</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3259</v>
+        <v>0.4237</v>
       </c>
       <c r="J116" t="n">
-        <v>7.1698</v>
+        <v>9.321400000000001</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0116</v>
+        <v>-0.0413</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.2552</v>
+        <v>-0.9086</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.85</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1889</v>
+        <v>-0.1597</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.1558</v>
+        <v>-3.5134</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2224</v>
+        <v>-0.1809</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.8928</v>
+        <v>-3.9798</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.59</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6107</v>
+        <v>-0.4084</v>
       </c>
       <c r="J120" t="n">
-        <v>-13.4354</v>
+        <v>-8.9848</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6107</v>
+        <v>-0.4084</v>
       </c>
       <c r="J121" t="n">
-        <v>-13.4354</v>
+        <v>-8.9848</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.59</v>
       </c>
       <c r="I122" t="n">
-        <v>1.415</v>
+        <v>1.2654</v>
       </c>
       <c r="J122" t="n">
-        <v>41.035</v>
+        <v>36.6966</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="J123" t="n">
-        <v>24.8646</v>
+        <v>24.65</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1101</v>
+        <v>-0.04</v>
       </c>
       <c r="J124" t="n">
-        <v>-3.1929</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1689</v>
+        <v>-0.0949</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.8981</v>
+        <v>-2.7521</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3791</v>
+        <v>-0.3053</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.9939</v>
+        <v>-8.8537</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2363</v>
+        <v>0.2521</v>
       </c>
       <c r="J127" t="n">
-        <v>6.8527</v>
+        <v>7.3109</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.145</v>
+        <v>0.144</v>
       </c>
       <c r="J128" t="n">
-        <v>4.205</v>
+        <v>4.176</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.053</v>
+        <v>0.0412</v>
       </c>
       <c r="J129" t="n">
-        <v>1.537</v>
+        <v>1.1948</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1846</v>
+        <v>-0.1093</v>
       </c>
       <c r="J130" t="n">
-        <v>-5.3534</v>
+        <v>-3.1697</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3637</v>
+        <v>-0.2264</v>
       </c>
       <c r="J131" t="n">
-        <v>-10.5473</v>
+        <v>-6.5656</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.31</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5612</v>
+        <v>0.6697</v>
       </c>
       <c r="J132" t="n">
-        <v>15.7136</v>
+        <v>18.7516</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.06</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1877</v>
+        <v>0.1828</v>
       </c>
       <c r="J133" t="n">
-        <v>5.2556</v>
+        <v>5.1184</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.91</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.175</v>
+        <v>-0.115</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.9</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.68</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.5306</v>
+        <v>-0.3457</v>
       </c>
       <c r="J135" t="n">
-        <v>-14.8568</v>
+        <v>-9.679600000000001</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.64</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5826</v>
+        <v>-0.3833</v>
       </c>
       <c r="J136" t="n">
-        <v>-16.3128</v>
+        <v>-10.7324</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.76</v>
       </c>
       <c r="I137" t="n">
-        <v>1.6642</v>
+        <v>1.4359</v>
       </c>
       <c r="J137" t="n">
-        <v>46.5976</v>
+        <v>40.2052</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.6836</v>
       </c>
       <c r="J138" t="n">
-        <v>16.9484</v>
+        <v>19.1408</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4552</v>
+        <v>0.5411</v>
       </c>
       <c r="J139" t="n">
-        <v>12.7456</v>
+        <v>15.1508</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.19</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4301</v>
+        <v>0.5164</v>
       </c>
       <c r="J140" t="n">
-        <v>12.0428</v>
+        <v>14.4592</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.194</v>
+        <v>0.2786</v>
       </c>
       <c r="J141" t="n">
-        <v>5.432</v>
+        <v>7.8008</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5246</v>
+        <v>0.6212</v>
       </c>
       <c r="J142" t="n">
-        <v>15.2134</v>
+        <v>18.0148</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.85</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.2138</v>
+        <v>-0.1674</v>
       </c>
       <c r="J143" t="n">
-        <v>-6.2002</v>
+        <v>-4.8546</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.72</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.444</v>
+        <v>-0.2929</v>
       </c>
       <c r="J144" t="n">
-        <v>-12.876</v>
+        <v>-8.4941</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.64</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.3687</v>
       </c>
       <c r="J145" t="n">
-        <v>-16.153</v>
+        <v>-10.6923</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.59</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6232</v>
+        <v>-0.4155</v>
       </c>
       <c r="J146" t="n">
-        <v>-18.0728</v>
+        <v>-12.0495</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9791</v>
+        <v>0.9881</v>
       </c>
       <c r="J147" t="n">
-        <v>28.3939</v>
+        <v>28.6549</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.36</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8902</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J148" t="n">
-        <v>25.8158</v>
+        <v>26.3842</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.34</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8442</v>
+        <v>0.866</v>
       </c>
       <c r="J149" t="n">
-        <v>24.4818</v>
+        <v>25.114</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.14</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3149</v>
+        <v>0.3955</v>
       </c>
       <c r="J150" t="n">
-        <v>9.132099999999999</v>
+        <v>11.4695</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.11</v>
       </c>
       <c r="I151" t="n">
-        <v>0.2337</v>
+        <v>0.3141</v>
       </c>
       <c r="J151" t="n">
-        <v>6.7773</v>
+        <v>9.1089</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5323</v>
+        <v>0.6301</v>
       </c>
       <c r="J152" t="n">
-        <v>18.6305</v>
+        <v>22.0535</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.95</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0882</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.087</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1995</v>
+        <v>-0.1266</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.9825</v>
+        <v>-4.431</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2701</v>
+        <v>-0.1691</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.4535</v>
+        <v>-5.9185</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.64</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.3842</v>
       </c>
       <c r="J156" t="n">
-        <v>-20.447</v>
+        <v>-13.447</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.7028</v>
       </c>
       <c r="J157" t="n">
-        <v>24.5035</v>
+        <v>24.598</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.25</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6751</v>
+        <v>0.6793</v>
       </c>
       <c r="J158" t="n">
-        <v>23.6285</v>
+        <v>23.7755</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.18</v>
       </c>
       <c r="I159" t="n">
-        <v>0.4699</v>
+        <v>0.5137</v>
       </c>
       <c r="J159" t="n">
-        <v>16.4465</v>
+        <v>17.9795</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4115</v>
+        <v>0.4642</v>
       </c>
       <c r="J160" t="n">
-        <v>14.4025</v>
+        <v>16.247</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.11</v>
       </c>
       <c r="I161" t="n">
-        <v>0.2692</v>
+        <v>0.3323</v>
       </c>
       <c r="J161" t="n">
-        <v>9.422000000000001</v>
+        <v>11.6305</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.01</v>
       </c>
       <c r="I162" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0594</v>
       </c>
       <c r="J162" t="n">
-        <v>2.2594</v>
+        <v>1.5444</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0316</v>
+        <v>-0.0408</v>
       </c>
       <c r="J163" t="n">
-        <v>-0.8216</v>
+        <v>-1.0608</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1152</v>
+        <v>-0.09130000000000001</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.9952</v>
+        <v>-2.3738</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3564</v>
+        <v>-0.2271</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.266400000000001</v>
+        <v>-5.9046</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.8</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3564</v>
+        <v>-0.2271</v>
       </c>
       <c r="J166" t="n">
-        <v>-9.266400000000001</v>
+        <v>-5.9046</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.54</v>
       </c>
       <c r="I167" t="n">
-        <v>1.282</v>
+        <v>1.1826</v>
       </c>
       <c r="J167" t="n">
-        <v>33.332</v>
+        <v>30.7476</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.4</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9948</v>
+        <v>0.9951</v>
       </c>
       <c r="J168" t="n">
-        <v>25.8648</v>
+        <v>25.8726</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.4623</v>
+        <v>0.5295</v>
       </c>
       <c r="J169" t="n">
-        <v>12.0198</v>
+        <v>13.767</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1301</v>
+        <v>0.2052</v>
       </c>
       <c r="J170" t="n">
-        <v>3.3826</v>
+        <v>5.3352</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.1373</v>
+        <v>-0.0585</v>
       </c>
       <c r="J171" t="n">
-        <v>-3.5698</v>
+        <v>-1.521</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.71</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9147</v>
+        <v>0.8324</v>
       </c>
       <c r="J172" t="n">
-        <v>22.8675</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4872</v>
+        <v>0.4362</v>
       </c>
       <c r="J173" t="n">
-        <v>12.18</v>
+        <v>10.905</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.3</v>
       </c>
       <c r="I174" t="n">
-        <v>0.432</v>
+        <v>0.3914</v>
       </c>
       <c r="J174" t="n">
-        <v>10.8</v>
+        <v>9.785</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.13</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1671</v>
+        <v>0.1862</v>
       </c>
       <c r="J175" t="n">
-        <v>4.1775</v>
+        <v>4.655</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3728</v>
+        <v>-0.2251</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.32</v>
+        <v>-5.6275</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.23</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4715</v>
+        <v>0.4179</v>
       </c>
       <c r="J177" t="n">
-        <v>11.7875</v>
+        <v>10.4475</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.93</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1007</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.5175</v>
+        <v>-2.1975</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3619</v>
+        <v>-0.2335</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.047499999999999</v>
+        <v>-5.8375</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4507</v>
+        <v>-0.292</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.2675</v>
+        <v>-7.3</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5063</v>
+        <v>-0.3303</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.6575</v>
+        <v>-8.2575</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.11</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2659</v>
+        <v>0.2828</v>
       </c>
       <c r="J182" t="n">
-        <v>7.4452</v>
+        <v>7.9184</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0483</v>
       </c>
       <c r="J183" t="n">
-        <v>1.932</v>
+        <v>1.3524</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.2071</v>
+        <v>-0.1282</v>
       </c>
       <c r="J184" t="n">
-        <v>-5.7988</v>
+        <v>-3.5896</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2595</v>
+        <v>-0.1604</v>
       </c>
       <c r="J185" t="n">
-        <v>-7.266</v>
+        <v>-4.4912</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3238</v>
+        <v>-0.202</v>
       </c>
       <c r="J186" t="n">
-        <v>-9.0664</v>
+        <v>-5.656</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.3532</v>
+        <v>1.225</v>
       </c>
       <c r="J187" t="n">
-        <v>37.8896</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0502</v>
+        <v>1.0281</v>
       </c>
       <c r="J188" t="n">
-        <v>29.4056</v>
+        <v>28.7868</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.83</v>
+        <v>0.8243</v>
       </c>
       <c r="J189" t="n">
-        <v>23.24</v>
+        <v>23.0804</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.93</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3818</v>
+        <v>-0.3073</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.6904</v>
+        <v>-8.6044</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.0356</v>
+        <v>-1.0149</v>
       </c>
       <c r="J191" t="n">
-        <v>-28.9968</v>
+        <v>-28.4172</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0434</v>
+        <v>1.2089</v>
       </c>
       <c r="J192" t="n">
-        <v>30.2586</v>
+        <v>35.0581</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.31</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5</v>
+        <v>0.6004</v>
       </c>
       <c r="J193" t="n">
-        <v>14.5</v>
+        <v>17.4116</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.2213</v>
+        <v>-0.1226</v>
       </c>
       <c r="J194" t="n">
-        <v>-6.4177</v>
+        <v>-3.5554</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.77</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.4452</v>
+        <v>-0.2799</v>
       </c>
       <c r="J195" t="n">
-        <v>-12.9108</v>
+        <v>-8.117100000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5111</v>
+        <v>-0.328</v>
       </c>
       <c r="J196" t="n">
-        <v>-14.8219</v>
+        <v>-9.512</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6496</v>
+        <v>0.6005</v>
       </c>
       <c r="J197" t="n">
-        <v>18.8384</v>
+        <v>17.4145</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5719</v>
+        <v>0.5205</v>
       </c>
       <c r="J198" t="n">
-        <v>16.5851</v>
+        <v>15.0945</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.98</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.1056</v>
+        <v>-0.0911</v>
       </c>
       <c r="J199" t="n">
-        <v>-3.0624</v>
+        <v>-2.6419</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.3279</v>
+        <v>-0.2868</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.5091</v>
+        <v>-8.3172</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.924</v>
+        <v>-0.8949</v>
       </c>
       <c r="J201" t="n">
-        <v>-26.796</v>
+        <v>-25.9521</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.43</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7175</v>
+        <v>0.891</v>
       </c>
       <c r="J202" t="n">
-        <v>17.9375</v>
+        <v>22.275</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.82</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.3246</v>
+        <v>-0.2068</v>
       </c>
       <c r="J203" t="n">
-        <v>-8.115</v>
+        <v>-5.17</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.3557</v>
+        <v>-0.2269</v>
       </c>
       <c r="J204" t="n">
-        <v>-8.8925</v>
+        <v>-5.6725</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.76</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.4152</v>
+        <v>-0.2663</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.38</v>
+        <v>-6.6575</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5128</v>
+        <v>-0.3337</v>
       </c>
       <c r="J206" t="n">
-        <v>-12.82</v>
+        <v>-8.342499999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.49</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1775</v>
+        <v>1.1174</v>
       </c>
       <c r="J207" t="n">
-        <v>29.4375</v>
+        <v>27.935</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.37</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9238</v>
+        <v>0.9358</v>
       </c>
       <c r="J208" t="n">
-        <v>23.095</v>
+        <v>23.395</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5091</v>
+        <v>0.576</v>
       </c>
       <c r="J209" t="n">
-        <v>12.7275</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.2</v>
       </c>
       <c r="I210" t="n">
-        <v>0.4827</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="J210" t="n">
-        <v>12.0675</v>
+        <v>13.7975</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2402</v>
+        <v>-0.1571</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.005</v>
+        <v>-3.9275</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.2021</v>
+        <v>-0.1731</v>
       </c>
       <c r="J212" t="n">
-        <v>-4.6483</v>
+        <v>-3.9813</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.82</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2184</v>
+        <v>-0.1838</v>
       </c>
       <c r="J213" t="n">
-        <v>-5.0232</v>
+        <v>-4.2274</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.466</v>
+        <v>-0.3181</v>
       </c>
       <c r="J214" t="n">
-        <v>-10.718</v>
+        <v>-7.3163</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.64</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.5271</v>
+        <v>-0.3554</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.1233</v>
+        <v>-8.174200000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.64</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.5271</v>
+        <v>-0.3554</v>
       </c>
       <c r="J216" t="n">
-        <v>-12.1233</v>
+        <v>-8.174200000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.63</v>
       </c>
       <c r="I217" t="n">
-        <v>1.3839</v>
+        <v>1.2605</v>
       </c>
       <c r="J217" t="n">
-        <v>31.8297</v>
+        <v>28.9915</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1262</v>
+        <v>1.1046</v>
       </c>
       <c r="J218" t="n">
-        <v>25.9026</v>
+        <v>25.4058</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.43</v>
       </c>
       <c r="I219" t="n">
-        <v>0.9736</v>
+        <v>1.015</v>
       </c>
       <c r="J219" t="n">
-        <v>22.3928</v>
+        <v>23.345</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.27</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5825</v>
+        <v>0.6882</v>
       </c>
       <c r="J220" t="n">
-        <v>13.3975</v>
+        <v>15.8286</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.15</v>
       </c>
       <c r="I221" t="n">
-        <v>0.295</v>
+        <v>0.3937</v>
       </c>
       <c r="J221" t="n">
-        <v>6.785</v>
+        <v>9.055099999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.34</v>
       </c>
       <c r="I222" t="n">
-        <v>0.957</v>
+        <v>0.9353</v>
       </c>
       <c r="J222" t="n">
-        <v>38.28</v>
+        <v>37.412</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.22</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6777</v>
+        <v>0.6449</v>
       </c>
       <c r="J223" t="n">
-        <v>27.108</v>
+        <v>25.796</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.05</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1619</v>
+        <v>0.1839</v>
       </c>
       <c r="J224" t="n">
-        <v>6.476</v>
+        <v>7.356</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3073</v>
+        <v>-0.2471</v>
       </c>
       <c r="J225" t="n">
-        <v>-12.292</v>
+        <v>-9.884</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7401</v>
+        <v>-0.6919999999999999</v>
       </c>
       <c r="J226" t="n">
-        <v>-29.604</v>
+        <v>-27.68</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.36</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5854</v>
+        <v>0.7067</v>
       </c>
       <c r="J227" t="n">
-        <v>23.416</v>
+        <v>28.268</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2143</v>
+        <v>0.2386</v>
       </c>
       <c r="J228" t="n">
-        <v>8.571999999999999</v>
+        <v>9.544</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1966</v>
+        <v>0.2184</v>
       </c>
       <c r="J229" t="n">
-        <v>7.864</v>
+        <v>8.736000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3327</v>
+        <v>-0.2022</v>
       </c>
       <c r="J230" t="n">
-        <v>-13.308</v>
+        <v>-8.087999999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.4192</v>
+        <v>-0.2628</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.768</v>
+        <v>-10.512</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.667</v>
+        <v>0.6384</v>
       </c>
       <c r="J232" t="n">
-        <v>17.342</v>
+        <v>16.5984</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.19</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5908</v>
+        <v>0.5629</v>
       </c>
       <c r="J233" t="n">
-        <v>15.3608</v>
+        <v>14.6354</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.12</v>
       </c>
       <c r="I234" t="n">
-        <v>0.396</v>
+        <v>0.38</v>
       </c>
       <c r="J234" t="n">
-        <v>10.296</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1311</v>
+        <v>-0.0735</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.4086</v>
+        <v>-1.911</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4361</v>
+        <v>-0.3728</v>
       </c>
       <c r="J236" t="n">
-        <v>-11.3386</v>
+        <v>-9.6928</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7471</v>
+        <v>0.9298</v>
       </c>
       <c r="J237" t="n">
-        <v>19.4246</v>
+        <v>24.1748</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.15</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3279</v>
+        <v>0.3614</v>
       </c>
       <c r="J238" t="n">
-        <v>8.525399999999999</v>
+        <v>9.3964</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.2267</v>
+        <v>-0.1395</v>
       </c>
       <c r="J239" t="n">
-        <v>-5.8942</v>
+        <v>-3.627</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.78</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.3996</v>
+        <v>-0.2527</v>
       </c>
       <c r="J240" t="n">
-        <v>-10.3896</v>
+        <v>-6.5702</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.8151</v>
+        <v>-0.5591</v>
       </c>
       <c r="J241" t="n">
-        <v>-21.1926</v>
+        <v>-14.5366</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3146</v>
+        <v>0.3394</v>
       </c>
       <c r="J242" t="n">
-        <v>8.8088</v>
+        <v>9.5032</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.93</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1141</v>
+        <v>-0.0911</v>
       </c>
       <c r="J243" t="n">
-        <v>-3.1948</v>
+        <v>-2.5508</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.91</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1549</v>
+        <v>-0.1137</v>
       </c>
       <c r="J244" t="n">
-        <v>-4.3372</v>
+        <v>-3.1836</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3403</v>
+        <v>-0.2169</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.5284</v>
+        <v>-6.0732</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.72</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4718</v>
+        <v>-0.305</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.2104</v>
+        <v>-8.539999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.4</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0457</v>
+        <v>1.0214</v>
       </c>
       <c r="J247" t="n">
-        <v>29.2796</v>
+        <v>28.5992</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.33</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8931</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J248" t="n">
-        <v>25.0068</v>
+        <v>24.6848</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.176</v>
+        <v>0.2288</v>
       </c>
       <c r="J249" t="n">
-        <v>4.928</v>
+        <v>6.4064</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.98</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2014</v>
+        <v>-0.1298</v>
       </c>
       <c r="J250" t="n">
-        <v>-5.6392</v>
+        <v>-3.6344</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3705</v>
+        <v>-0.299</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.374</v>
+        <v>-8.372</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.93</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.073</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.679</v>
+        <v>-1.8009</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.86</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1984</v>
+        <v>-0.1575</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.5632</v>
+        <v>-3.6225</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.82</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.272</v>
+        <v>-0.1979</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.256</v>
+        <v>-4.5517</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.77</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3683</v>
+        <v>-0.2455</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.4709</v>
+        <v>-5.6465</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4889</v>
+        <v>-0.322</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.2447</v>
+        <v>-7.406</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.71</v>
       </c>
       <c r="I257" t="n">
-        <v>1.5787</v>
+        <v>1.3786</v>
       </c>
       <c r="J257" t="n">
-        <v>36.3101</v>
+        <v>31.7078</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.34</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8304</v>
+        <v>0.8613</v>
       </c>
       <c r="J258" t="n">
-        <v>19.0992</v>
+        <v>19.8099</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.34</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8304</v>
+        <v>0.8613</v>
       </c>
       <c r="J259" t="n">
-        <v>19.0992</v>
+        <v>19.8099</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.31</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7558</v>
+        <v>0.7956</v>
       </c>
       <c r="J260" t="n">
-        <v>17.3834</v>
+        <v>18.2988</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.76</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.8415</v>
+        <v>-0.7968</v>
       </c>
       <c r="J261" t="n">
-        <v>-19.3545</v>
+        <v>-18.3264</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2130/event_2130_evp_summary.xlsx
+++ b/database/event/2130/event_2130_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7043</v>
+        <v>7.7144</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9554</v>
+        <v>2.9592</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8401</v>
+        <v>2.8876</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7043</v>
+        <v>7.7144</v>
       </c>
       <c r="F2" t="n">
-        <v>3.043</v>
+        <v>2.9332</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6613</v>
+        <v>4.7812</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2355</v>
+        <v>4.7834</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7222</v>
+        <v>2.583</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6613</v>
+        <v>4.7812</v>
       </c>
       <c r="K2" t="n">
         <v>167</v>
@@ -529,7 +529,7 @@
         <v>213</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3835</v>
+        <v>7.3642</v>
       </c>
       <c r="N2" t="n">
         <v>380</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6441</v>
+        <v>6.9296</v>
       </c>
       <c r="C3" t="n">
-        <v>2.5487</v>
+        <v>2.6582</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3615</v>
+        <v>2.5303</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6441</v>
+        <v>6.9296</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7035</v>
+        <v>3.6368</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9406</v>
+        <v>3.2928</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5624</v>
+        <v>7.1051</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9321</v>
+        <v>3.8367</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9406</v>
+        <v>3.2928</v>
       </c>
       <c r="K3" t="n">
         <v>167</v>
@@ -575,7 +575,7 @@
         <v>213</v>
       </c>
       <c r="M3" t="n">
-        <v>6.8727</v>
+        <v>7.1295</v>
       </c>
       <c r="N3" t="n">
         <v>380</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2738</v>
+        <v>6.3099</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4066</v>
+        <v>2.4205</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1943</v>
+        <v>2.2482</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2738</v>
+        <v>6.3099</v>
       </c>
       <c r="F4" t="n">
-        <v>2.414</v>
+        <v>2.3219</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8598</v>
+        <v>3.988</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0191</v>
+        <v>2.7665</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5698</v>
+        <v>1.4939</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8598</v>
+        <v>3.988</v>
       </c>
       <c r="K4" t="n">
         <v>51</v>
@@ -621,7 +621,7 @@
         <v>225</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4296</v>
+        <v>5.4819</v>
       </c>
       <c r="N4" t="n">
         <v>276</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.4526</v>
+        <v>5.3474</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0916</v>
+        <v>2.0513</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8236</v>
+        <v>1.81</v>
       </c>
       <c r="E5" t="n">
-        <v>5.4526</v>
+        <v>5.3474</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9649</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4877</v>
+        <v>4.4932</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9649</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5017</v>
+        <v>0.4613</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4877</v>
+        <v>4.4932</v>
       </c>
       <c r="K5" t="n">
         <v>167</v>
@@ -667,7 +667,7 @@
         <v>213</v>
       </c>
       <c r="M5" t="n">
-        <v>4.9894</v>
+        <v>4.954499999999999</v>
       </c>
       <c r="N5" t="n">
         <v>380</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.5007</v>
+        <v>4.4166</v>
       </c>
       <c r="C6" t="n">
-        <v>1.7265</v>
+        <v>1.6942</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3938</v>
+        <v>1.3863</v>
       </c>
       <c r="E6" t="n">
-        <v>4.5007</v>
+        <v>4.4166</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8748</v>
+        <v>1.7543</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6259</v>
+        <v>2.6623</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8748</v>
+        <v>1.7543</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9748</v>
+        <v>0.9473</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6259</v>
+        <v>2.6623</v>
       </c>
       <c r="K6" t="n">
         <v>51</v>
@@ -713,7 +713,7 @@
         <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6007</v>
+        <v>3.6096</v>
       </c>
       <c r="N6" t="n">
         <v>276</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5888</v>
+        <v>3.642</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3767</v>
+        <v>1.3971</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9822</v>
+        <v>1.0337</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5888</v>
+        <v>3.642</v>
       </c>
       <c r="F7" t="n">
-        <v>2.176</v>
+        <v>1.9493</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4128</v>
+        <v>1.6927</v>
       </c>
       <c r="H7" t="n">
-        <v>2.1804</v>
+        <v>1.9493</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1337</v>
+        <v>1.0526</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4128</v>
+        <v>1.6927</v>
       </c>
       <c r="K7" t="n">
         <v>167</v>
@@ -759,7 +759,7 @@
         <v>213</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5465</v>
+        <v>2.7453</v>
       </c>
       <c r="N7" t="n">
         <v>380</v>
@@ -768,93 +768,93 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5685</v>
+        <v>3.5702</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3689</v>
+        <v>1.3695</v>
       </c>
       <c r="D8" t="n">
-        <v>0.973</v>
+        <v>1.001</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5685</v>
+        <v>3.5702</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3279</v>
+        <v>2.5674</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2406</v>
+        <v>1.0028</v>
       </c>
       <c r="H8" t="n">
-        <v>6.2392</v>
+        <v>3.5767</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2441</v>
+        <v>1.9314</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2406</v>
+        <v>1.0028</v>
       </c>
       <c r="K8" t="n">
-        <v>102</v>
+        <v>51</v>
       </c>
       <c r="L8" t="n">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4847</v>
+        <v>2.9342</v>
       </c>
       <c r="N8" t="n">
-        <v>184</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.534</v>
+        <v>3.5701</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3556</v>
+        <v>1.3695</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9574</v>
+        <v>1.001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.534</v>
+        <v>3.5701</v>
       </c>
       <c r="F9" t="n">
-        <v>2.6687</v>
+        <v>3.2419</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8653</v>
+        <v>0.3282</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9165</v>
+        <v>5.8021</v>
       </c>
       <c r="I9" t="n">
-        <v>2.0364</v>
+        <v>3.1331</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8653</v>
+        <v>0.3282</v>
       </c>
       <c r="K9" t="n">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="L9" t="n">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9017</v>
+        <v>3.4613</v>
       </c>
       <c r="N9" t="n">
-        <v>276</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4904</v>
+        <v>2.369</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9553</v>
+        <v>0.9087</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4863</v>
+        <v>0.4542</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4904</v>
+        <v>2.369</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4555</v>
+        <v>2.3577</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0349</v>
+        <v>0.0113</v>
       </c>
       <c r="H10" t="n">
-        <v>3.1653</v>
+        <v>2.8847</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6458</v>
+        <v>1.5577</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0349</v>
+        <v>0.0113</v>
       </c>
       <c r="K10" t="n">
         <v>102</v>
@@ -897,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>1.6807</v>
+        <v>1.569</v>
       </c>
       <c r="N10" t="n">
         <v>184</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2813</v>
+        <v>2.2539</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8751</v>
+        <v>0.8646</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3919</v>
+        <v>0.4018</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2813</v>
+        <v>2.2539</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8492</v>
+        <v>1.7647</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4321</v>
+        <v>0.4892</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8492</v>
+        <v>1.7647</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9615</v>
+        <v>0.9529</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4321</v>
+        <v>0.4892</v>
       </c>
       <c r="K11" t="n">
         <v>51</v>
@@ -943,7 +943,7 @@
         <v>225</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3936</v>
+        <v>1.4421</v>
       </c>
       <c r="N11" t="n">
         <v>276</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0113</v>
+        <v>1.9681</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7715</v>
+        <v>0.755</v>
       </c>
       <c r="D12" t="n">
-        <v>0.27</v>
+        <v>0.2717</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0113</v>
+        <v>1.9681</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0113</v>
+        <v>1.9681</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0113</v>
+        <v>1.9681</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0113</v>
+        <v>1.9681</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.0113</v>
+        <v>1.9681</v>
       </c>
       <c r="N12" t="n">
         <v>105</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9478</v>
+        <v>1.8238</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7472</v>
+        <v>0.6996</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2413</v>
+        <v>0.206</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9478</v>
+        <v>1.8238</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9478</v>
+        <v>1.8238</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9478</v>
+        <v>1.8238</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9478</v>
+        <v>1.8238</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.9478</v>
+        <v>1.8238</v>
       </c>
       <c r="N13" t="n">
         <v>152</v>
@@ -1044,185 +1044,185 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8041</v>
+        <v>1.7281</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6921</v>
+        <v>0.6629</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1764</v>
+        <v>0.1625</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8041</v>
+        <v>1.7281</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2104</v>
+        <v>1.5159</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4063</v>
+        <v>0.2122</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3017</v>
+        <v>1.5159</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1968</v>
+        <v>0.8186</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4063</v>
+        <v>0.2122</v>
       </c>
       <c r="K14" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="L14" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7905000000000001</v>
+        <v>1.0308</v>
       </c>
       <c r="N14" t="n">
-        <v>135</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7716</v>
+        <v>1.7152</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6796</v>
+        <v>0.6579</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1618</v>
+        <v>0.1566</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7716</v>
+        <v>1.7152</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5582</v>
+        <v>2.1307</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2134</v>
+        <v>-0.4155</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5582</v>
+        <v>2.1358</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8102</v>
+        <v>1.1533</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2134</v>
+        <v>-0.4155</v>
       </c>
       <c r="K15" t="n">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="L15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0236</v>
+        <v>0.7378</v>
       </c>
       <c r="N15" t="n">
-        <v>184</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7461</v>
+        <v>1.6697</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6698</v>
+        <v>0.6405</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1503</v>
+        <v>0.1359</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7461</v>
+        <v>1.6697</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6738</v>
+        <v>1.6697</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0723</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6738</v>
+        <v>1.6697</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8703</v>
+        <v>1.6697</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0723</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>65</v>
+        <v>152</v>
       </c>
       <c r="L16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9426</v>
+        <v>1.6697</v>
       </c>
       <c r="N16" t="n">
-        <v>135</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7089</v>
+        <v>1.6339</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6555</v>
+        <v>0.6268</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1335</v>
+        <v>0.1196</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7089</v>
+        <v>1.6339</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7089</v>
+        <v>1.5511</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.0828</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7089</v>
+        <v>1.5511</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7089</v>
+        <v>0.8376</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>0.0828</v>
       </c>
       <c r="K17" t="n">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>1.7089</v>
+        <v>0.9204</v>
       </c>
       <c r="N17" t="n">
-        <v>152</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18">
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5669</v>
+        <v>1.4564</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6011</v>
+        <v>0.5587</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0694</v>
+        <v>0.0388</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5669</v>
+        <v>1.4564</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3821</v>
+        <v>2.2864</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8152</v>
+        <v>-0.83</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9066</v>
+        <v>2.6495</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5113</v>
+        <v>1.4307</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8152</v>
+        <v>-0.83</v>
       </c>
       <c r="K18" t="n">
         <v>65</v>
@@ -1265,7 +1265,7 @@
         <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.6007000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>135</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0509</v>
+        <v>1.0211</v>
       </c>
       <c r="C19" t="n">
-        <v>0.4031</v>
+        <v>0.3917</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1636</v>
+        <v>-0.1594</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0509</v>
+        <v>1.0211</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0509</v>
+        <v>1.0211</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0509</v>
+        <v>1.0211</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0509</v>
+        <v>1.0211</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0509</v>
+        <v>1.0211</v>
       </c>
       <c r="N19" t="n">
         <v>87</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0082</v>
+        <v>0.8972</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3867</v>
+        <v>0.3442</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1829</v>
+        <v>-0.2158</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0082</v>
+        <v>0.8972</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0082</v>
+        <v>0.8972</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0082</v>
+        <v>0.8972</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0082</v>
+        <v>0.8972</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.0082</v>
+        <v>0.8972</v>
       </c>
       <c r="N20" t="n">
         <v>103</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.953</v>
+        <v>0.8378</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3656</v>
+        <v>0.3214</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2078</v>
+        <v>-0.2428</v>
       </c>
       <c r="E21" t="n">
-        <v>0.953</v>
+        <v>0.8378</v>
       </c>
       <c r="F21" t="n">
-        <v>0.953</v>
+        <v>0.8378</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.953</v>
+        <v>0.8378</v>
       </c>
       <c r="I21" t="n">
-        <v>0.953</v>
+        <v>0.8378</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.953</v>
+        <v>0.8378</v>
       </c>
       <c r="N21" t="n">
         <v>103</v>
@@ -1412,93 +1412,93 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>wenton</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.7266</v>
       </c>
       <c r="C22" t="n">
-        <v>0.3177</v>
+        <v>0.2787</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2642</v>
+        <v>-0.2934</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.7266</v>
       </c>
       <c r="F22" t="n">
-        <v>1.032</v>
+        <v>0.7266</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2039</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.032</v>
+        <v>0.7266</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5366</v>
+        <v>0.7266</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2039</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="L22" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3327</v>
+        <v>0.7266</v>
       </c>
       <c r="N22" t="n">
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>wenton</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7332</v>
+        <v>0.6849</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2813</v>
+        <v>0.2627</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.307</v>
+        <v>-0.3124</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7332</v>
+        <v>0.6849</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7332</v>
+        <v>0.8911</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.2062</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7332</v>
+        <v>0.8911</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7332</v>
+        <v>0.4812</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.2062</v>
       </c>
       <c r="K23" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7332</v>
+        <v>0.275</v>
       </c>
       <c r="N23" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24">
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7218</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2769</v>
+        <v>0.2508</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3122</v>
+        <v>-0.3266</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7218</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7218</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7218</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7218</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7218</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>103</v>
@@ -1550,139 +1550,139 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6694</v>
+        <v>0.611</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2568</v>
+        <v>0.2344</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3358</v>
+        <v>-0.3461</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6694</v>
+        <v>0.611</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6694</v>
+        <v>0.0883</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6694</v>
+        <v>0.0883</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6694</v>
+        <v>0.0477</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M25" t="n">
-        <v>0.6694</v>
+        <v>0.5704</v>
       </c>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6473</v>
+        <v>0.5855</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2483</v>
+        <v>0.2246</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3458</v>
+        <v>-0.3577</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6473</v>
+        <v>0.5855</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0822</v>
+        <v>0.5855</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4349</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1.0822</v>
+        <v>0.5855</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5627</v>
+        <v>0.5855</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4349</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="L26" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1278</v>
+        <v>0.5855</v>
       </c>
       <c r="N26" t="n">
-        <v>184</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5614</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2154</v>
+        <v>0.2032</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3846</v>
+        <v>-0.3831</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5614</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0515</v>
+        <v>0.9858</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5099</v>
+        <v>-0.4561</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0515</v>
+        <v>0.9858</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0268</v>
+        <v>0.5323</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5099</v>
+        <v>-0.4561</v>
       </c>
       <c r="K27" t="n">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="L27" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5367000000000001</v>
+        <v>0.07619999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>135</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4133</v>
+        <v>0.3572</v>
       </c>
       <c r="C28" t="n">
-        <v>0.1585</v>
+        <v>0.137</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4514</v>
+        <v>-0.4616</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4133</v>
+        <v>0.3572</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4133</v>
+        <v>0.3572</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4133</v>
+        <v>0.3572</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4133</v>
+        <v>0.3572</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.4133</v>
+        <v>0.3572</v>
       </c>
       <c r="N28" t="n">
         <v>152</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3446</v>
+        <v>0.3074</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1322</v>
+        <v>0.1179</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4824</v>
+        <v>-0.4843</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3446</v>
+        <v>0.3074</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3446</v>
+        <v>0.3074</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3446</v>
+        <v>0.3074</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3446</v>
+        <v>0.3074</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3446</v>
+        <v>0.3074</v>
       </c>
       <c r="N29" t="n">
         <v>152</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.1942</v>
+        <v>0.2116</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0745</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5503</v>
+        <v>-0.5279</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1942</v>
+        <v>0.2116</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1972</v>
+        <v>1.1885</v>
       </c>
       <c r="G30" t="n">
-        <v>-1.003</v>
+        <v>-0.9769</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1972</v>
+        <v>1.1885</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.6418</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.003</v>
+        <v>-0.9769</v>
       </c>
       <c r="K30" t="n">
         <v>51</v>
@@ -1817,7 +1817,7 @@
         <v>225</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3804999999999998</v>
+        <v>-0.3351</v>
       </c>
       <c r="N30" t="n">
         <v>276</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1936</v>
+        <v>0.1799</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0743</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5506</v>
+        <v>-0.5423</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1936</v>
+        <v>0.1799</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1936</v>
+        <v>0.1799</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1936</v>
+        <v>0.1799</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1936</v>
+        <v>0.1799</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1936</v>
+        <v>0.1799</v>
       </c>
       <c r="N31" t="n">
         <v>105</v>
@@ -1872,32 +1872,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>dupreeh</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0246</v>
+        <v>-0.0755</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0094</v>
+        <v>-0.029</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6491</v>
+        <v>-0.6586</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0246</v>
+        <v>-0.0755</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0246</v>
+        <v>-0.0755</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0246</v>
+        <v>-0.0755</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0246</v>
+        <v>-0.0755</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0246</v>
+        <v>-0.0755</v>
       </c>
       <c r="N32" t="n">
         <v>105</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dupreeh</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.0491</v>
+        <v>-0.078</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0188</v>
+        <v>-0.0299</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6602</v>
+        <v>-0.6597</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0491</v>
+        <v>-0.078</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.0491</v>
+        <v>-0.078</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.0491</v>
+        <v>-0.078</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0491</v>
+        <v>-0.078</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0491</v>
+        <v>-0.078</v>
       </c>
       <c r="N33" t="n">
         <v>105</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.236</v>
+        <v>-0.319</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0905</v>
+        <v>-0.1224</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7446</v>
+        <v>-0.7694</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.236</v>
+        <v>-0.319</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.236</v>
+        <v>-0.319</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.236</v>
+        <v>-0.319</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.236</v>
+        <v>-0.319</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.236</v>
+        <v>-0.319</v>
       </c>
       <c r="N34" t="n">
         <v>103</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3465</v>
+        <v>-0.3843</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1329</v>
+        <v>-0.1474</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7944</v>
+        <v>-0.7991</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3465</v>
+        <v>-0.3843</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4689</v>
+        <v>0.435</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8154</v>
+        <v>-0.8193</v>
       </c>
       <c r="H35" t="n">
-        <v>0.4689</v>
+        <v>0.435</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2438</v>
+        <v>0.2349</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8154</v>
+        <v>-0.8193</v>
       </c>
       <c r="K35" t="n">
         <v>65</v>
@@ -2047,7 +2047,7 @@
         <v>70</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5716</v>
+        <v>-0.5844</v>
       </c>
       <c r="N35" t="n">
         <v>135</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.3635</v>
+        <v>-0.4</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1394</v>
+        <v>-0.1534</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8021</v>
+        <v>-0.8063</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.3635</v>
+        <v>-0.4</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.3635</v>
+        <v>-0.4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.3635</v>
+        <v>-0.4</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3635</v>
+        <v>-0.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.3635</v>
+        <v>-0.4</v>
       </c>
       <c r="N36" t="n">
         <v>87</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.4932</v>
+        <v>-0.538</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1892</v>
+        <v>-0.2064</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8607</v>
+        <v>-0.8691</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.4932</v>
+        <v>-0.538</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4932</v>
+        <v>-0.538</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4932</v>
+        <v>-0.538</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4932</v>
+        <v>-0.538</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.4932</v>
+        <v>-0.538</v>
       </c>
       <c r="N37" t="n">
         <v>87</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.592</v>
+        <v>-0.6122</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2271</v>
+        <v>-0.2348</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9053</v>
+        <v>-0.9029</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.592</v>
+        <v>-0.6122</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.592</v>
+        <v>-0.6122</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.592</v>
+        <v>-0.6122</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.592</v>
+        <v>-0.6122</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.592</v>
+        <v>-0.6122</v>
       </c>
       <c r="N38" t="n">
         <v>105</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>-1.1998</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.4602</v>
+      </c>
+      <c r="D39" t="n">
         <v>-1.1704</v>
       </c>
-      <c r="C39" t="n">
-        <v>-0.449</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-1.1664</v>
-      </c>
       <c r="E39" t="n">
-        <v>-1.1704</v>
+        <v>-1.1998</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1704</v>
+        <v>-1.1998</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1704</v>
+        <v>-1.1998</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1704</v>
+        <v>-1.1998</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1704</v>
+        <v>-1.1998</v>
       </c>
       <c r="N39" t="n">
         <v>87</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3476</v>
+        <v>-1.3092</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5169</v>
+        <v>-0.5022</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2464</v>
+        <v>-1.2202</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3476</v>
+        <v>-1.3092</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3476</v>
+        <v>-1.3092</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3476</v>
+        <v>-1.3092</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3476</v>
+        <v>-1.3092</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3476</v>
+        <v>-1.3092</v>
       </c>
       <c r="N40" t="n">
         <v>103</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9315</v>
+        <v>-1.7848</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.7409</v>
+        <v>-0.6846</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.51</v>
+        <v>-1.4367</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9315</v>
+        <v>-1.7848</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.2892</v>
+        <v>-1.1969</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.6423</v>
+        <v>-0.5879</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.2892</v>
+        <v>-1.1969</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6703</v>
+        <v>-0.6463</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.6423</v>
+        <v>-0.5879</v>
       </c>
       <c r="K41" t="n">
         <v>167</v>
@@ -2323,7 +2323,7 @@
         <v>213</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.3126</v>
+        <v>-1.2342</v>
       </c>
       <c r="N41" t="n">
         <v>380</v>
@@ -2429,10 +2429,10 @@
         <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4007</v>
+        <v>0.3993</v>
       </c>
       <c r="J2" t="n">
-        <v>10.4182</v>
+        <v>10.3818</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1955</v>
+        <v>0.203</v>
       </c>
       <c r="J3" t="n">
-        <v>5.083</v>
+        <v>5.278</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0337</v>
+        <v>-0.041</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8762</v>
+        <v>-1.066</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.245</v>
+        <v>-0.2591</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.37</v>
+        <v>-6.7366</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3132</v>
+        <v>-0.3261</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.1432</v>
+        <v>-8.4786</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8363</v>
+        <v>0.8204</v>
       </c>
       <c r="J7" t="n">
-        <v>21.7438</v>
+        <v>21.3304</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2477</v>
+        <v>0.2649</v>
       </c>
       <c r="J8" t="n">
-        <v>6.4402</v>
+        <v>6.8874</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.07</v>
       </c>
       <c r="I9" t="n">
-        <v>0.112</v>
+        <v>0.1284</v>
       </c>
       <c r="J9" t="n">
-        <v>2.912</v>
+        <v>3.3384</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0072</v>
+        <v>0.0175</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1872</v>
+        <v>0.455</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1521</v>
+        <v>-0.1609</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.9546</v>
+        <v>-4.1834</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3184</v>
+        <v>1.3916</v>
       </c>
       <c r="J12" t="n">
-        <v>38.2336</v>
+        <v>40.3564</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8759</v>
+        <v>0.8227</v>
       </c>
       <c r="J13" t="n">
-        <v>25.4011</v>
+        <v>23.8583</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1627</v>
+        <v>0.1767</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7183</v>
+        <v>5.1243</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.89</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4215</v>
+        <v>-0.399</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.2235</v>
+        <v>-11.571</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4215</v>
+        <v>-0.399</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.2235</v>
+        <v>-11.571</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9308</v>
+        <v>0.8758</v>
       </c>
       <c r="J17" t="n">
-        <v>26.9932</v>
+        <v>25.3982</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0318</v>
+        <v>-0.0396</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.9222</v>
+        <v>-1.1484</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2225</v>
+        <v>-0.2374</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.4525</v>
+        <v>-6.8846</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2819</v>
+        <v>-0.2959</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.1751</v>
+        <v>-8.581099999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3108</v>
+        <v>-0.3242</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.013199999999999</v>
+        <v>-9.4018</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.99</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0076</v>
+        <v>-0.0052</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1976</v>
+        <v>-0.1352</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.92</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0907</v>
+        <v>-0.1076</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3582</v>
+        <v>-2.7976</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.198</v>
+        <v>-0.2163</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.148</v>
+        <v>-5.6238</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2842</v>
+        <v>-0.3015</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.3892</v>
+        <v>-7.839</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3883</v>
+        <v>-0.4019</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.0958</v>
+        <v>-10.4494</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.65</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7575</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>19.695</v>
+        <v>19.591</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4301</v>
+        <v>0.4458</v>
       </c>
       <c r="J28" t="n">
-        <v>11.1826</v>
+        <v>11.5908</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.28</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3645</v>
+        <v>0.3824</v>
       </c>
       <c r="J29" t="n">
-        <v>9.477</v>
+        <v>9.942399999999999</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.27</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3531</v>
+        <v>0.3713</v>
       </c>
       <c r="J30" t="n">
-        <v>9.1806</v>
+        <v>9.6538</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.09</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1229</v>
+        <v>0.1444</v>
       </c>
       <c r="J31" t="n">
-        <v>3.1954</v>
+        <v>3.7544</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.89</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6238</v>
+        <v>1.7537</v>
       </c>
       <c r="J32" t="n">
-        <v>43.8426</v>
+        <v>47.3499</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.39</v>
       </c>
       <c r="I33" t="n">
-        <v>0.9879</v>
+        <v>0.931</v>
       </c>
       <c r="J33" t="n">
-        <v>26.6733</v>
+        <v>25.137</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.36</v>
       </c>
       <c r="I34" t="n">
-        <v>0.929</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>25.083</v>
+        <v>23.5575</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5159</v>
+        <v>-0.4827</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.9293</v>
+        <v>-13.0329</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.5</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3898</v>
+        <v>-1.2454</v>
       </c>
       <c r="J36" t="n">
-        <v>-37.5246</v>
+        <v>-33.6258</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.24</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5333</v>
+        <v>0.5169</v>
       </c>
       <c r="J37" t="n">
-        <v>14.3991</v>
+        <v>13.9563</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.92</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1058</v>
+        <v>-0.1191</v>
       </c>
       <c r="J38" t="n">
-        <v>-2.8566</v>
+        <v>-3.2157</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.89</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1388</v>
+        <v>-0.1533</v>
       </c>
       <c r="J39" t="n">
-        <v>-3.7476</v>
+        <v>-4.1391</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1496</v>
+        <v>-0.1642</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.0392</v>
+        <v>-4.4334</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.252</v>
+        <v>-0.2666</v>
       </c>
       <c r="J41" t="n">
-        <v>-6.804</v>
+        <v>-7.1982</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.44</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0548</v>
+        <v>1.0164</v>
       </c>
       <c r="J42" t="n">
-        <v>36.918</v>
+        <v>35.574</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.41</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0112</v>
+        <v>0.9597</v>
       </c>
       <c r="J43" t="n">
-        <v>35.392</v>
+        <v>33.5895</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.34</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8729</v>
+        <v>0.8247</v>
       </c>
       <c r="J44" t="n">
-        <v>30.5515</v>
+        <v>28.8645</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1089</v>
+        <v>0.1306</v>
       </c>
       <c r="J45" t="n">
-        <v>3.8115</v>
+        <v>4.571</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.98</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1551</v>
+        <v>-0.1422</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.4285</v>
+        <v>-4.977</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5244</v>
+        <v>0.507</v>
       </c>
       <c r="J47" t="n">
-        <v>18.354</v>
+        <v>17.745</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.11</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2909</v>
+        <v>0.2896</v>
       </c>
       <c r="J48" t="n">
-        <v>10.1815</v>
+        <v>10.136</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.85</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1786</v>
+        <v>-0.1942</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.251</v>
+        <v>-6.797</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2193</v>
+        <v>-0.235</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.6755</v>
+        <v>-8.225</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4204</v>
+        <v>-0.4302</v>
       </c>
       <c r="J51" t="n">
-        <v>-14.714</v>
+        <v>-15.057</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2417</v>
+        <v>0.2446</v>
       </c>
       <c r="J52" t="n">
-        <v>7.251</v>
+        <v>7.338</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.99</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0112</v>
+        <v>-0.0181</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.336</v>
+        <v>-0.543</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0272</v>
+        <v>-0.036</v>
       </c>
       <c r="J54" t="n">
-        <v>-0.8159999999999999</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2179</v>
+        <v>-0.2338</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.537</v>
+        <v>-7.014</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3818</v>
+        <v>-0.3936</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.454</v>
+        <v>-11.808</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.92</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.8838</v>
       </c>
       <c r="J57" t="n">
-        <v>23.181</v>
+        <v>26.514</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.12</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1839</v>
+        <v>0.2011</v>
       </c>
       <c r="J58" t="n">
-        <v>5.517</v>
+        <v>6.033</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.01</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0078</v>
+        <v>0.0179</v>
       </c>
       <c r="J59" t="n">
-        <v>0.234</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1517</v>
+        <v>-0.1606</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.551</v>
+        <v>-4.818</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1845</v>
+        <v>-0.1939</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.535</v>
+        <v>-5.817</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.78</v>
       </c>
       <c r="I62" t="n">
-        <v>1.1755</v>
+        <v>1.2904</v>
       </c>
       <c r="J62" t="n">
-        <v>28.212</v>
+        <v>30.9696</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9609</v>
+        <v>1.0627</v>
       </c>
       <c r="J63" t="n">
-        <v>23.0616</v>
+        <v>25.5048</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I64" t="n">
-        <v>0.7023</v>
+        <v>0.783</v>
       </c>
       <c r="J64" t="n">
-        <v>16.8552</v>
+        <v>18.792</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.15</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3762</v>
+        <v>0.4113</v>
       </c>
       <c r="J65" t="n">
-        <v>9.0288</v>
+        <v>9.8712</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7315</v>
+        <v>-0.6699000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-17.556</v>
+        <v>-16.0776</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2202</v>
+        <v>0.2128</v>
       </c>
       <c r="J67" t="n">
-        <v>5.2848</v>
+        <v>5.1072</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0475</v>
+        <v>0.0344</v>
       </c>
       <c r="J68" t="n">
-        <v>1.14</v>
+        <v>0.8256</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.86</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1586</v>
+        <v>-0.1764</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.8064</v>
+        <v>-4.2336</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3891</v>
+        <v>-0.4025</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.3384</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4357</v>
+        <v>-0.4469</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.4568</v>
+        <v>-10.7256</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6947</v>
+        <v>0.7677</v>
       </c>
       <c r="J72" t="n">
-        <v>19.4516</v>
+        <v>21.4956</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4577</v>
+        <v>0.5052</v>
       </c>
       <c r="J73" t="n">
-        <v>12.8156</v>
+        <v>14.1456</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4432</v>
+        <v>0.4888</v>
       </c>
       <c r="J74" t="n">
-        <v>12.4096</v>
+        <v>13.6864</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2558</v>
+        <v>0.2642</v>
       </c>
       <c r="J75" t="n">
-        <v>7.1624</v>
+        <v>7.3976</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.96</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.2052</v>
+        <v>-0.1971</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.7456</v>
+        <v>-5.5188</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3697</v>
+        <v>0.3902</v>
       </c>
       <c r="J77" t="n">
-        <v>10.3516</v>
+        <v>10.9256</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.018</v>
+        <v>-0.0233</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.504</v>
+        <v>-0.6524</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0336</v>
+        <v>-0.0409</v>
       </c>
       <c r="J79" t="n">
-        <v>-0.9408</v>
+        <v>-1.1452</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0964</v>
+        <v>-0.1087</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.6992</v>
+        <v>-3.0436</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2841</v>
+        <v>-0.2976</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.9548</v>
+        <v>-8.332800000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.93</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0265</v>
+        <v>-0.0541</v>
       </c>
       <c r="J82" t="n">
-        <v>-0.53</v>
+        <v>-1.082</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0527</v>
+        <v>-0.0806</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.054</v>
+        <v>-1.612</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.62</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3604</v>
+        <v>-0.3802</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.208</v>
+        <v>-7.604</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4996</v>
+        <v>-0.5115</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.992000000000001</v>
+        <v>-10.23</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.24</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7181</v>
+        <v>-0.7126</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.362</v>
+        <v>-14.252</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.95</v>
       </c>
       <c r="I87" t="n">
-        <v>1.3248</v>
+        <v>1.4549</v>
       </c>
       <c r="J87" t="n">
-        <v>26.496</v>
+        <v>29.098</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.79</v>
       </c>
       <c r="I88" t="n">
-        <v>1.1465</v>
+        <v>1.2669</v>
       </c>
       <c r="J88" t="n">
-        <v>22.93</v>
+        <v>25.338</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.48</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7935</v>
+        <v>0.8872</v>
       </c>
       <c r="J89" t="n">
-        <v>15.87</v>
+        <v>17.744</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.32</v>
       </c>
       <c r="I90" t="n">
-        <v>0.5924</v>
+        <v>0.6669</v>
       </c>
       <c r="J90" t="n">
-        <v>11.848</v>
+        <v>13.338</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.18</v>
       </c>
       <c r="I91" t="n">
-        <v>0.3968</v>
+        <v>0.4471</v>
       </c>
       <c r="J91" t="n">
-        <v>7.936</v>
+        <v>8.942</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4174</v>
+        <v>0.4725</v>
       </c>
       <c r="J92" t="n">
-        <v>10.0176</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.26</v>
       </c>
       <c r="I93" t="n">
-        <v>0.348</v>
+        <v>0.3726</v>
       </c>
       <c r="J93" t="n">
-        <v>8.352</v>
+        <v>8.942399999999999</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1711</v>
+        <v>0.188</v>
       </c>
       <c r="J94" t="n">
-        <v>4.1064</v>
+        <v>4.512</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.1</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1572</v>
+        <v>0.174</v>
       </c>
       <c r="J95" t="n">
-        <v>3.7728</v>
+        <v>4.176</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.092</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.208</v>
+        <v>-2.3664</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.25</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3911</v>
+        <v>0.4233</v>
       </c>
       <c r="J97" t="n">
-        <v>9.3864</v>
+        <v>10.1592</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.081</v>
+        <v>-0.0936</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.944</v>
+        <v>-2.2464</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1147</v>
+        <v>-0.129</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.7528</v>
+        <v>-3.096</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2189</v>
+        <v>-0.2346</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.2536</v>
+        <v>-5.6304</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3546</v>
+        <v>-0.3673</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.510400000000001</v>
+        <v>-8.815200000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4054</v>
+        <v>0.4293</v>
       </c>
       <c r="J102" t="n">
-        <v>10.5404</v>
+        <v>11.1618</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.98</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0051</v>
+        <v>-0.0188</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.1326</v>
+        <v>-0.4888</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3186</v>
+        <v>-0.3356</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.2836</v>
+        <v>-8.7256</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3939</v>
+        <v>-0.4079</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.2414</v>
+        <v>-10.6054</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4869</v>
+        <v>-0.4958</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.6594</v>
+        <v>-12.8908</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.6</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9535</v>
+        <v>1.0562</v>
       </c>
       <c r="J107" t="n">
-        <v>24.791</v>
+        <v>27.4612</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7718</v>
+        <v>0.8601</v>
       </c>
       <c r="J108" t="n">
-        <v>20.0668</v>
+        <v>22.3626</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7229</v>
+        <v>0.8066</v>
       </c>
       <c r="J109" t="n">
-        <v>18.7954</v>
+        <v>20.9716</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.33</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6239</v>
+        <v>0.6973</v>
       </c>
       <c r="J110" t="n">
-        <v>16.2214</v>
+        <v>18.1298</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.12</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3155</v>
+        <v>0.3323</v>
       </c>
       <c r="J111" t="n">
-        <v>8.202999999999999</v>
+        <v>8.639799999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.88</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5567</v>
+        <v>1.5521</v>
       </c>
       <c r="J112" t="n">
-        <v>34.2474</v>
+        <v>34.1462</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9118000000000001</v>
+        <v>0.8642</v>
       </c>
       <c r="J113" t="n">
-        <v>20.0596</v>
+        <v>19.0124</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.28</v>
       </c>
       <c r="I114" t="n">
-        <v>0.7149</v>
+        <v>0.6901</v>
       </c>
       <c r="J114" t="n">
-        <v>15.7278</v>
+        <v>15.1822</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5248</v>
+        <v>0.5209</v>
       </c>
       <c r="J115" t="n">
-        <v>11.5456</v>
+        <v>11.4598</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.16</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4237</v>
+        <v>0.4298</v>
       </c>
       <c r="J116" t="n">
-        <v>9.321400000000001</v>
+        <v>9.4556</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0413</v>
+        <v>-0.0593</v>
       </c>
       <c r="J117" t="n">
-        <v>-0.9086</v>
+        <v>-1.3046</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.85</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1597</v>
+        <v>-0.1797</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.5134</v>
+        <v>-3.9534</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1809</v>
+        <v>-0.2008</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.9798</v>
+        <v>-4.4176</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.59</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4084</v>
+        <v>-0.4224</v>
       </c>
       <c r="J120" t="n">
-        <v>-8.9848</v>
+        <v>-9.2928</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4084</v>
+        <v>-0.4224</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.9848</v>
+        <v>-9.2928</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.59</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2654</v>
+        <v>1.2349</v>
       </c>
       <c r="J122" t="n">
-        <v>36.6966</v>
+        <v>35.8121</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.85</v>
+        <v>0.8006</v>
       </c>
       <c r="J123" t="n">
-        <v>24.65</v>
+        <v>23.2174</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.04</v>
+        <v>-0.0275</v>
       </c>
       <c r="J124" t="n">
-        <v>-1.16</v>
+        <v>-0.7975</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0949</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.7521</v>
+        <v>-2.5346</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3053</v>
+        <v>-0.291</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.8537</v>
+        <v>-8.439</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2521</v>
+        <v>0.2567</v>
       </c>
       <c r="J127" t="n">
-        <v>7.3109</v>
+        <v>7.4443</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.144</v>
+        <v>0.1513</v>
       </c>
       <c r="J128" t="n">
-        <v>4.176</v>
+        <v>4.3877</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0412</v>
+        <v>0.0458</v>
       </c>
       <c r="J129" t="n">
-        <v>1.1948</v>
+        <v>1.3282</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1093</v>
+        <v>-0.1218</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.1697</v>
+        <v>-3.5322</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2264</v>
+        <v>-0.2404</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.5656</v>
+        <v>-6.9716</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.31</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6697</v>
+        <v>0.6391</v>
       </c>
       <c r="J132" t="n">
-        <v>18.7516</v>
+        <v>17.8948</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.06</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1828</v>
+        <v>0.1854</v>
       </c>
       <c r="J133" t="n">
-        <v>5.1184</v>
+        <v>5.1912</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.91</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.115</v>
+        <v>-0.1292</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.22</v>
+        <v>-3.6176</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.68</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3457</v>
+        <v>-0.3586</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.679600000000001</v>
+        <v>-10.0408</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.64</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3833</v>
+        <v>-0.3947</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.7324</v>
+        <v>-11.0516</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.76</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4359</v>
+        <v>1.4219</v>
       </c>
       <c r="J137" t="n">
-        <v>40.2052</v>
+        <v>39.8132</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6836</v>
+        <v>0.6595</v>
       </c>
       <c r="J138" t="n">
-        <v>19.1408</v>
+        <v>18.466</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5411</v>
+        <v>0.5322</v>
       </c>
       <c r="J139" t="n">
-        <v>15.1508</v>
+        <v>14.9016</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.19</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5164</v>
+        <v>0.51</v>
       </c>
       <c r="J140" t="n">
-        <v>14.4592</v>
+        <v>14.28</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2786</v>
+        <v>0.2936</v>
       </c>
       <c r="J141" t="n">
-        <v>7.8008</v>
+        <v>8.220800000000001</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.6212</v>
+        <v>0.5851</v>
       </c>
       <c r="J142" t="n">
-        <v>18.0148</v>
+        <v>16.9679</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.85</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1674</v>
+        <v>-0.1857</v>
       </c>
       <c r="J143" t="n">
-        <v>-4.8546</v>
+        <v>-5.3853</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.72</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2929</v>
+        <v>-0.3102</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.4941</v>
+        <v>-8.995799999999999</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.64</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3687</v>
+        <v>-0.3833</v>
       </c>
       <c r="J145" t="n">
-        <v>-10.6923</v>
+        <v>-11.1157</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.59</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4155</v>
+        <v>-0.4279</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.0495</v>
+        <v>-12.4091</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9881</v>
+        <v>0.9342</v>
       </c>
       <c r="J147" t="n">
-        <v>28.6549</v>
+        <v>27.0918</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.36</v>
       </c>
       <c r="I148" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8586</v>
       </c>
       <c r="J148" t="n">
-        <v>26.3842</v>
+        <v>24.8994</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.34</v>
       </c>
       <c r="I149" t="n">
-        <v>0.866</v>
+        <v>0.82</v>
       </c>
       <c r="J149" t="n">
-        <v>25.114</v>
+        <v>23.78</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.14</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3955</v>
+        <v>0.3991</v>
       </c>
       <c r="J150" t="n">
-        <v>11.4695</v>
+        <v>11.5739</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.11</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3141</v>
+        <v>0.3247</v>
       </c>
       <c r="J151" t="n">
-        <v>9.1089</v>
+        <v>9.4163</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6301</v>
+        <v>0.6039</v>
       </c>
       <c r="J152" t="n">
-        <v>22.0535</v>
+        <v>21.1365</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.95</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.45</v>
+        <v>-2.856</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1266</v>
+        <v>-0.141</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.431</v>
+        <v>-4.935</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1691</v>
+        <v>-0.1845</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.9185</v>
+        <v>-6.4575</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.64</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3842</v>
+        <v>-0.3955</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.447</v>
+        <v>-13.8425</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7028</v>
+        <v>0.6725</v>
       </c>
       <c r="J157" t="n">
-        <v>24.598</v>
+        <v>23.5375</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.25</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6793</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="J158" t="n">
-        <v>23.7755</v>
+        <v>22.8095</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.18</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5137</v>
+        <v>0.5028</v>
       </c>
       <c r="J159" t="n">
-        <v>17.9795</v>
+        <v>17.598</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4642</v>
+        <v>0.4579</v>
       </c>
       <c r="J160" t="n">
-        <v>16.247</v>
+        <v>16.0265</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.11</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3323</v>
+        <v>0.3373</v>
       </c>
       <c r="J161" t="n">
-        <v>11.6305</v>
+        <v>11.8055</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.01</v>
       </c>
       <c r="I162" t="n">
-        <v>0.0594</v>
+        <v>0.059</v>
       </c>
       <c r="J162" t="n">
-        <v>1.5444</v>
+        <v>1.534</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0408</v>
+        <v>-0.0512</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.0608</v>
+        <v>-1.3312</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.1049</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.3738</v>
+        <v>-2.7274</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2271</v>
+        <v>-0.2432</v>
       </c>
       <c r="J165" t="n">
-        <v>-5.9046</v>
+        <v>-6.3232</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.8</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2271</v>
+        <v>-0.2432</v>
       </c>
       <c r="J166" t="n">
-        <v>-5.9046</v>
+        <v>-6.3232</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.54</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1826</v>
+        <v>1.1502</v>
       </c>
       <c r="J167" t="n">
-        <v>30.7476</v>
+        <v>29.9052</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.4</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9951</v>
+        <v>0.9401</v>
       </c>
       <c r="J168" t="n">
-        <v>25.8726</v>
+        <v>24.4426</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.5295</v>
+        <v>0.519</v>
       </c>
       <c r="J169" t="n">
-        <v>13.767</v>
+        <v>13.494</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2052</v>
+        <v>0.2219</v>
       </c>
       <c r="J170" t="n">
-        <v>5.3352</v>
+        <v>5.7694</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0585</v>
+        <v>-0.0405</v>
       </c>
       <c r="J171" t="n">
-        <v>-1.521</v>
+        <v>-1.053</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.71</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8324</v>
+        <v>0.8205</v>
       </c>
       <c r="J172" t="n">
-        <v>20.81</v>
+        <v>20.5125</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4362</v>
+        <v>0.4504</v>
       </c>
       <c r="J173" t="n">
-        <v>10.905</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.3</v>
       </c>
       <c r="I174" t="n">
-        <v>0.3914</v>
+        <v>0.4074</v>
       </c>
       <c r="J174" t="n">
-        <v>9.785</v>
+        <v>10.185</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.13</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1862</v>
+        <v>0.2061</v>
       </c>
       <c r="J175" t="n">
-        <v>4.655</v>
+        <v>5.1525</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2251</v>
+        <v>-0.2329</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.6275</v>
+        <v>-5.8225</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.23</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4179</v>
+        <v>0.4097</v>
       </c>
       <c r="J177" t="n">
-        <v>10.4475</v>
+        <v>10.2425</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.93</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.1023</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.1975</v>
+        <v>-2.5575</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2335</v>
+        <v>-0.2502</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.8375</v>
+        <v>-6.255</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.292</v>
+        <v>-0.3076</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.3</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3303</v>
+        <v>-0.3447</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.2575</v>
+        <v>-8.6175</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.11</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2828</v>
+        <v>0.2837</v>
       </c>
       <c r="J182" t="n">
-        <v>7.9184</v>
+        <v>7.9436</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0483</v>
+        <v>0.0509</v>
       </c>
       <c r="J183" t="n">
-        <v>1.3524</v>
+        <v>1.4252</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1282</v>
+        <v>-0.1423</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.5896</v>
+        <v>-3.9844</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1604</v>
+        <v>-0.1752</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.4912</v>
+        <v>-4.9056</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.202</v>
+        <v>-0.217</v>
       </c>
       <c r="J186" t="n">
-        <v>-5.656</v>
+        <v>-6.076</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.225</v>
+        <v>1.1922</v>
       </c>
       <c r="J187" t="n">
-        <v>34.3</v>
+        <v>33.3816</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>1.0281</v>
+        <v>0.973</v>
       </c>
       <c r="J188" t="n">
-        <v>28.7868</v>
+        <v>27.244</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.8243</v>
+        <v>0.7785</v>
       </c>
       <c r="J189" t="n">
-        <v>23.0804</v>
+        <v>21.798</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.93</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3073</v>
+        <v>-0.2925</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.6044</v>
+        <v>-8.19</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-1.0149</v>
+        <v>-0.9244</v>
       </c>
       <c r="J191" t="n">
-        <v>-28.4172</v>
+        <v>-25.8832</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.2089</v>
+        <v>1.1915</v>
       </c>
       <c r="J192" t="n">
-        <v>35.0581</v>
+        <v>34.5535</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.31</v>
       </c>
       <c r="I193" t="n">
-        <v>0.6004</v>
+        <v>0.5881</v>
       </c>
       <c r="J193" t="n">
-        <v>17.4116</v>
+        <v>17.0549</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1226</v>
+        <v>-0.1321</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.5554</v>
+        <v>-3.8309</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.77</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2799</v>
+        <v>-0.2905</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.117100000000001</v>
+        <v>-8.4245</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.328</v>
+        <v>-0.3377</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.512</v>
+        <v>-9.7933</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.6005</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J197" t="n">
-        <v>17.4145</v>
+        <v>16.472</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.5205</v>
+        <v>0.4967</v>
       </c>
       <c r="J198" t="n">
-        <v>15.0945</v>
+        <v>14.4043</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.98</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0911</v>
+        <v>-0.0978</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.6419</v>
+        <v>-2.8362</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2868</v>
+        <v>-0.2854</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.3172</v>
+        <v>-8.2766</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.8949</v>
+        <v>-0.828</v>
       </c>
       <c r="J201" t="n">
-        <v>-25.9521</v>
+        <v>-24.012</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.43</v>
       </c>
       <c r="I202" t="n">
-        <v>0.891</v>
+        <v>0.8354</v>
       </c>
       <c r="J202" t="n">
-        <v>22.275</v>
+        <v>20.885</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.82</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2068</v>
+        <v>-0.2231</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.17</v>
+        <v>-5.5775</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.2269</v>
+        <v>-0.243</v>
       </c>
       <c r="J204" t="n">
-        <v>-5.6725</v>
+        <v>-6.075</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.76</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2663</v>
+        <v>-0.2818</v>
       </c>
       <c r="J205" t="n">
-        <v>-6.6575</v>
+        <v>-7.045</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3337</v>
+        <v>-0.3474</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.342499999999999</v>
+        <v>-8.685</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.49</v>
       </c>
       <c r="I207" t="n">
-        <v>1.1174</v>
+        <v>1.0805</v>
       </c>
       <c r="J207" t="n">
-        <v>27.935</v>
+        <v>27.0125</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.37</v>
       </c>
       <c r="I208" t="n">
-        <v>0.9358</v>
+        <v>0.8815</v>
       </c>
       <c r="J208" t="n">
-        <v>23.395</v>
+        <v>22.0375</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.576</v>
+        <v>0.5613</v>
       </c>
       <c r="J209" t="n">
-        <v>14.4</v>
+        <v>14.0325</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.2</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.5396</v>
       </c>
       <c r="J210" t="n">
-        <v>13.7975</v>
+        <v>13.49</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1571</v>
+        <v>-0.1435</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.9275</v>
+        <v>-3.5875</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1731</v>
+        <v>-0.1948</v>
       </c>
       <c r="J212" t="n">
-        <v>-3.9813</v>
+        <v>-4.4804</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.82</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.1838</v>
+        <v>-0.2054</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.2274</v>
+        <v>-4.7242</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3181</v>
+        <v>-0.3371</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.3163</v>
+        <v>-7.7533</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.64</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3554</v>
+        <v>-0.3729</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.174200000000001</v>
+        <v>-8.576700000000001</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.64</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3554</v>
+        <v>-0.3729</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.174200000000001</v>
+        <v>-8.576700000000001</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.63</v>
       </c>
       <c r="I217" t="n">
-        <v>1.2605</v>
+        <v>1.2395</v>
       </c>
       <c r="J217" t="n">
-        <v>28.9915</v>
+        <v>28.5085</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.1046</v>
+        <v>1.0718</v>
       </c>
       <c r="J218" t="n">
-        <v>25.4058</v>
+        <v>24.6514</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.43</v>
       </c>
       <c r="I219" t="n">
-        <v>1.015</v>
+        <v>0.968</v>
       </c>
       <c r="J219" t="n">
-        <v>23.345</v>
+        <v>22.264</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.27</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6882</v>
+        <v>0.6672</v>
       </c>
       <c r="J220" t="n">
-        <v>15.8286</v>
+        <v>15.3456</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.15</v>
       </c>
       <c r="I221" t="n">
-        <v>0.3937</v>
+        <v>0.4035</v>
       </c>
       <c r="J221" t="n">
-        <v>9.055099999999999</v>
+        <v>9.2805</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.34</v>
       </c>
       <c r="I222" t="n">
-        <v>0.9353</v>
+        <v>0.8694</v>
       </c>
       <c r="J222" t="n">
-        <v>37.412</v>
+        <v>34.776</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.22</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6449</v>
+        <v>0.6137</v>
       </c>
       <c r="J223" t="n">
-        <v>25.796</v>
+        <v>24.548</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.05</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1839</v>
+        <v>0.1912</v>
       </c>
       <c r="J224" t="n">
-        <v>7.356</v>
+        <v>7.648</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2471</v>
+        <v>-0.2429</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.884</v>
+        <v>-9.715999999999999</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6919999999999999</v>
+        <v>-0.6466</v>
       </c>
       <c r="J226" t="n">
-        <v>-27.68</v>
+        <v>-25.864</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.36</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7067</v>
+        <v>0.6806</v>
       </c>
       <c r="J227" t="n">
-        <v>28.268</v>
+        <v>27.224</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2386</v>
+        <v>0.2469</v>
       </c>
       <c r="J228" t="n">
-        <v>9.544</v>
+        <v>9.875999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2184</v>
+        <v>0.2273</v>
       </c>
       <c r="J229" t="n">
-        <v>8.736000000000001</v>
+        <v>9.092000000000001</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2022</v>
+        <v>-0.2149</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.087999999999999</v>
+        <v>-8.596</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2628</v>
+        <v>-0.2751</v>
       </c>
       <c r="J231" t="n">
-        <v>-10.512</v>
+        <v>-11.004</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6384</v>
+        <v>0.6091</v>
       </c>
       <c r="J232" t="n">
-        <v>16.5984</v>
+        <v>15.8366</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.19</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5629</v>
+        <v>0.5419</v>
       </c>
       <c r="J233" t="n">
-        <v>14.6354</v>
+        <v>14.0894</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.12</v>
       </c>
       <c r="I234" t="n">
-        <v>0.38</v>
+        <v>0.3762</v>
       </c>
       <c r="J234" t="n">
-        <v>9.880000000000001</v>
+        <v>9.7812</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0735</v>
+        <v>-0.0725</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.911</v>
+        <v>-1.885</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3728</v>
+        <v>-0.3586</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.6928</v>
+        <v>-9.323600000000001</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>0.9298</v>
+        <v>0.8749</v>
       </c>
       <c r="J237" t="n">
-        <v>24.1748</v>
+        <v>22.7474</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.15</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3614</v>
+        <v>0.3582</v>
       </c>
       <c r="J238" t="n">
-        <v>9.3964</v>
+        <v>9.3132</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1395</v>
+        <v>-0.1538</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.627</v>
+        <v>-3.9988</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.78</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2527</v>
+        <v>-0.2672</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.5702</v>
+        <v>-6.9472</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5591</v>
+        <v>-0.5611</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.5366</v>
+        <v>-14.5886</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3394</v>
+        <v>0.3339</v>
       </c>
       <c r="J242" t="n">
-        <v>9.5032</v>
+        <v>9.3492</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.93</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0911</v>
+        <v>-0.1047</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.5508</v>
+        <v>-2.9316</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.91</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1137</v>
+        <v>-0.1283</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.1836</v>
+        <v>-3.5924</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2169</v>
+        <v>-0.233</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.0732</v>
+        <v>-6.524</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.72</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.305</v>
+        <v>-0.3196</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.539999999999999</v>
+        <v>-8.9488</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.4</v>
       </c>
       <c r="I247" t="n">
-        <v>1.0214</v>
+        <v>0.9634</v>
       </c>
       <c r="J247" t="n">
-        <v>28.5992</v>
+        <v>26.9752</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.33</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.8267</v>
       </c>
       <c r="J248" t="n">
-        <v>24.6848</v>
+        <v>23.1476</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2288</v>
+        <v>0.2383</v>
       </c>
       <c r="J249" t="n">
-        <v>6.4064</v>
+        <v>6.6724</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.98</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1298</v>
+        <v>-0.1245</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.6344</v>
+        <v>-3.486</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.299</v>
+        <v>-0.2866</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.372</v>
+        <v>-8.024800000000001</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.93</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.07829999999999999</v>
+        <v>-0.0948</v>
       </c>
       <c r="J252" t="n">
-        <v>-1.8009</v>
+        <v>-2.1804</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.86</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1575</v>
+        <v>-0.1756</v>
       </c>
       <c r="J253" t="n">
-        <v>-3.6225</v>
+        <v>-4.0388</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.82</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1979</v>
+        <v>-0.2162</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.5517</v>
+        <v>-4.9726</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.77</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2455</v>
+        <v>-0.2637</v>
       </c>
       <c r="J255" t="n">
-        <v>-5.6465</v>
+        <v>-6.0651</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.322</v>
+        <v>-0.3383</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.406</v>
+        <v>-7.7809</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.71</v>
       </c>
       <c r="I257" t="n">
-        <v>1.3786</v>
+        <v>1.361</v>
       </c>
       <c r="J257" t="n">
-        <v>31.7078</v>
+        <v>31.303</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.34</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8613</v>
+        <v>0.8167</v>
       </c>
       <c r="J258" t="n">
-        <v>19.8099</v>
+        <v>18.7841</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.34</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8613</v>
+        <v>0.8167</v>
       </c>
       <c r="J259" t="n">
-        <v>19.8099</v>
+        <v>18.7841</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.31</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7956</v>
+        <v>0.7588</v>
       </c>
       <c r="J260" t="n">
-        <v>18.2988</v>
+        <v>17.4524</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.76</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7968</v>
+        <v>-0.7296</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.3264</v>
+        <v>-16.7808</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/2130/event_2130_evp_summary.xlsx
+++ b/database/event/2130/event_2130_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.7144</v>
+        <v>7.7239</v>
       </c>
       <c r="C2" t="n">
-        <v>2.9592</v>
+        <v>2.9629</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8876</v>
+        <v>2.9128</v>
       </c>
       <c r="E2" t="n">
-        <v>7.7144</v>
+        <v>7.7239</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9332</v>
+        <v>2.9208</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7812</v>
+        <v>4.8031</v>
       </c>
       <c r="H2" t="n">
-        <v>4.7834</v>
+        <v>4.5235</v>
       </c>
       <c r="I2" t="n">
-        <v>2.583</v>
+        <v>2.5398</v>
       </c>
       <c r="J2" t="n">
-        <v>4.7812</v>
+        <v>4.8031</v>
       </c>
       <c r="K2" t="n">
         <v>167</v>
@@ -529,7 +529,7 @@
         <v>213</v>
       </c>
       <c r="M2" t="n">
-        <v>7.3642</v>
+        <v>7.3429</v>
       </c>
       <c r="N2" t="n">
         <v>380</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.9296</v>
+        <v>6.8507</v>
       </c>
       <c r="C3" t="n">
-        <v>2.6582</v>
+        <v>2.6279</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5303</v>
+        <v>2.515</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9296</v>
+        <v>6.8507</v>
       </c>
       <c r="F3" t="n">
-        <v>3.6368</v>
+        <v>3.4785</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2928</v>
+        <v>3.3722</v>
       </c>
       <c r="H3" t="n">
-        <v>7.1051</v>
+        <v>6.6173</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8367</v>
+        <v>3.7154</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2928</v>
+        <v>3.3722</v>
       </c>
       <c r="K3" t="n">
         <v>167</v>
@@ -575,7 +575,7 @@
         <v>213</v>
       </c>
       <c r="M3" t="n">
-        <v>7.1295</v>
+        <v>7.0876</v>
       </c>
       <c r="N3" t="n">
         <v>380</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.3099</v>
+        <v>6.1577</v>
       </c>
       <c r="C4" t="n">
-        <v>2.4205</v>
+        <v>2.3621</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2482</v>
+        <v>2.1993</v>
       </c>
       <c r="E4" t="n">
-        <v>6.3099</v>
+        <v>6.1577</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3219</v>
+        <v>2.4027</v>
       </c>
       <c r="G4" t="n">
-        <v>3.988</v>
+        <v>3.755</v>
       </c>
       <c r="H4" t="n">
-        <v>2.7665</v>
+        <v>2.5782</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4939</v>
+        <v>1.4476</v>
       </c>
       <c r="J4" t="n">
-        <v>3.988</v>
+        <v>3.755</v>
       </c>
       <c r="K4" t="n">
         <v>51</v>
@@ -621,7 +621,7 @@
         <v>225</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4819</v>
+        <v>5.2026</v>
       </c>
       <c r="N4" t="n">
         <v>276</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3474</v>
+        <v>5.377</v>
       </c>
       <c r="C5" t="n">
-        <v>2.0513</v>
+        <v>2.0626</v>
       </c>
       <c r="D5" t="n">
-        <v>1.81</v>
+        <v>1.8437</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3474</v>
+        <v>5.377</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.8804</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4932</v>
+        <v>4.4966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8542999999999999</v>
+        <v>0.8804</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4613</v>
+        <v>0.4943</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4932</v>
+        <v>4.4966</v>
       </c>
       <c r="K5" t="n">
         <v>167</v>
@@ -667,7 +667,7 @@
         <v>213</v>
       </c>
       <c r="M5" t="n">
-        <v>4.954499999999999</v>
+        <v>4.9909</v>
       </c>
       <c r="N5" t="n">
         <v>380</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.4166</v>
+        <v>4.2706</v>
       </c>
       <c r="C6" t="n">
-        <v>1.6942</v>
+        <v>1.6382</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3863</v>
+        <v>1.3397</v>
       </c>
       <c r="E6" t="n">
-        <v>4.4166</v>
+        <v>4.2706</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7543</v>
+        <v>1.7577</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6623</v>
+        <v>2.5129</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7543</v>
+        <v>1.7577</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9473</v>
+        <v>0.9869</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6623</v>
+        <v>2.5129</v>
       </c>
       <c r="K6" t="n">
         <v>51</v>
@@ -713,7 +713,7 @@
         <v>225</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6096</v>
+        <v>3.4998</v>
       </c>
       <c r="N6" t="n">
         <v>276</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>RpK</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.642</v>
+        <v>3.5881</v>
       </c>
       <c r="C7" t="n">
-        <v>1.3971</v>
+        <v>1.3764</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0337</v>
+        <v>1.0288</v>
       </c>
       <c r="E7" t="n">
-        <v>3.642</v>
+        <v>3.5881</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9493</v>
+        <v>2.6271</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6927</v>
+        <v>0.961</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9493</v>
+        <v>3.4207</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0526</v>
+        <v>1.9206</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6927</v>
+        <v>0.961</v>
       </c>
       <c r="K7" t="n">
-        <v>167</v>
+        <v>51</v>
       </c>
       <c r="L7" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7453</v>
+        <v>2.8816</v>
       </c>
       <c r="N7" t="n">
-        <v>380</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RpK</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5702</v>
+        <v>3.5187</v>
       </c>
       <c r="C8" t="n">
-        <v>1.3695</v>
+        <v>1.3498</v>
       </c>
       <c r="D8" t="n">
-        <v>1.001</v>
+        <v>0.9971</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5702</v>
+        <v>3.5187</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5674</v>
+        <v>1.8861</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0028</v>
+        <v>1.6326</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5767</v>
+        <v>1.8861</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9314</v>
+        <v>1.059</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0028</v>
+        <v>1.6326</v>
       </c>
       <c r="K8" t="n">
-        <v>51</v>
+        <v>167</v>
       </c>
       <c r="L8" t="n">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="M8" t="n">
-        <v>2.9342</v>
+        <v>2.6916</v>
       </c>
       <c r="N8" t="n">
-        <v>276</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5701</v>
+        <v>3.4602</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3695</v>
+        <v>1.3273</v>
       </c>
       <c r="D9" t="n">
-        <v>1.001</v>
+        <v>0.9705</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5701</v>
+        <v>3.4602</v>
       </c>
       <c r="F9" t="n">
-        <v>3.2419</v>
+        <v>3.1586</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3282</v>
+        <v>0.3016</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8021</v>
+        <v>5.416</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1331</v>
+        <v>3.0409</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3282</v>
+        <v>0.3016</v>
       </c>
       <c r="K9" t="n">
         <v>102</v>
@@ -851,7 +851,7 @@
         <v>82</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4613</v>
+        <v>3.3425</v>
       </c>
       <c r="N9" t="n">
         <v>184</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.369</v>
+        <v>2.4201</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9087</v>
+        <v>0.9283</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4542</v>
+        <v>0.4967</v>
       </c>
       <c r="E10" t="n">
-        <v>2.369</v>
+        <v>2.4201</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3577</v>
+        <v>2.4191</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0113</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8847</v>
+        <v>2.6399</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5577</v>
+        <v>1.4822</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0113</v>
+        <v>0.001</v>
       </c>
       <c r="K10" t="n">
         <v>102</v>
@@ -897,7 +897,7 @@
         <v>82</v>
       </c>
       <c r="M10" t="n">
-        <v>1.569</v>
+        <v>1.4832</v>
       </c>
       <c r="N10" t="n">
         <v>184</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2539</v>
+        <v>2.2153</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8646</v>
+        <v>0.8498</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4018</v>
+        <v>0.4034</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2539</v>
+        <v>2.2153</v>
       </c>
       <c r="F11" t="n">
-        <v>1.7647</v>
+        <v>1.7997</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4892</v>
+        <v>0.4156</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7647</v>
+        <v>1.7997</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9529</v>
+        <v>1.0105</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4892</v>
+        <v>0.4156</v>
       </c>
       <c r="K11" t="n">
         <v>51</v>
@@ -943,7 +943,7 @@
         <v>225</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4421</v>
+        <v>1.4261</v>
       </c>
       <c r="N11" t="n">
         <v>276</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9681</v>
+        <v>1.8701</v>
       </c>
       <c r="C12" t="n">
-        <v>0.755</v>
+        <v>0.7174</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2717</v>
+        <v>0.2461</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9681</v>
+        <v>1.8701</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9681</v>
+        <v>1.8701</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9681</v>
+        <v>1.8701</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9681</v>
+        <v>1.8701</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9681</v>
+        <v>1.8701</v>
       </c>
       <c r="N12" t="n">
         <v>105</v>
@@ -998,127 +998,127 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.8238</v>
+        <v>1.8061</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6996</v>
+        <v>0.6928</v>
       </c>
       <c r="D13" t="n">
-        <v>0.206</v>
+        <v>0.217</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8238</v>
+        <v>1.8061</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8238</v>
+        <v>1.6348</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.1713</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8238</v>
+        <v>1.6348</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8238</v>
+        <v>0.9179</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>0.1713</v>
       </c>
       <c r="K13" t="n">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="M13" t="n">
-        <v>1.8238</v>
+        <v>1.0892</v>
       </c>
       <c r="N13" t="n">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7281</v>
+        <v>1.7475</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6629</v>
+        <v>0.6703</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1625</v>
+        <v>0.1903</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7281</v>
+        <v>1.7475</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5159</v>
+        <v>1.7475</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2122</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5159</v>
+        <v>1.7475</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8186</v>
+        <v>1.7475</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2122</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="L14" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0308</v>
+        <v>1.7475</v>
       </c>
       <c r="N14" t="n">
-        <v>184</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Xizt</t>
+          <t>f0rest</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7152</v>
+        <v>1.6409</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6579</v>
+        <v>0.6294</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1566</v>
+        <v>0.1417</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7152</v>
+        <v>1.6409</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1307</v>
+        <v>1.5776</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4155</v>
+        <v>0.0633</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1358</v>
+        <v>1.5776</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1533</v>
+        <v>0.8858</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4155</v>
+        <v>0.0633</v>
       </c>
       <c r="K15" t="n">
         <v>65</v>
@@ -1127,7 +1127,7 @@
         <v>70</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7378</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="N15" t="n">
         <v>135</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.6697</v>
+        <v>1.5655</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6405</v>
+        <v>0.6005</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1359</v>
+        <v>0.1074</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6697</v>
+        <v>1.5655</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6697</v>
+        <v>1.5655</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6697</v>
+        <v>1.5655</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6697</v>
+        <v>1.5655</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6697</v>
+        <v>1.5655</v>
       </c>
       <c r="N16" t="n">
         <v>152</v>
@@ -1182,35 +1182,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>f0rest</t>
+          <t>pyth</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6339</v>
+        <v>1.531</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6268</v>
+        <v>0.5873</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1196</v>
+        <v>0.0917</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6339</v>
+        <v>1.531</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5511</v>
+        <v>2.37</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0828</v>
+        <v>-0.839</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5511</v>
+        <v>2.4555</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8376</v>
+        <v>1.3787</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0828</v>
+        <v>-0.839</v>
       </c>
       <c r="K17" t="n">
         <v>65</v>
@@ -1219,7 +1219,7 @@
         <v>70</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9204</v>
+        <v>0.5397000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>135</v>
@@ -1228,35 +1228,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>pyth</t>
+          <t>Xizt</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.4564</v>
+        <v>1.4748</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5587</v>
+        <v>0.5657</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0388</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4564</v>
+        <v>1.4748</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2864</v>
+        <v>1.9301</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.83</v>
+        <v>-0.4553</v>
       </c>
       <c r="H18" t="n">
-        <v>2.6495</v>
+        <v>1.9301</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4307</v>
+        <v>1.0837</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.83</v>
+        <v>-0.4553</v>
       </c>
       <c r="K18" t="n">
         <v>65</v>
@@ -1265,7 +1265,7 @@
         <v>70</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6007000000000001</v>
+        <v>0.6284000000000001</v>
       </c>
       <c r="N18" t="n">
         <v>135</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0211</v>
+        <v>0.8865</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3917</v>
+        <v>0.3401</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1594</v>
+        <v>-0.2019</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0211</v>
+        <v>0.8865</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0211</v>
+        <v>0.8865</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0211</v>
+        <v>0.8865</v>
       </c>
       <c r="I19" t="n">
-        <v>1.0211</v>
+        <v>0.8865</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0211</v>
+        <v>0.8865</v>
       </c>
       <c r="N19" t="n">
         <v>87</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8972</v>
+        <v>0.8501</v>
       </c>
       <c r="C20" t="n">
-        <v>0.3442</v>
+        <v>0.3261</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2158</v>
+        <v>-0.2185</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8972</v>
+        <v>0.8501</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8972</v>
+        <v>0.8501</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8972</v>
+        <v>0.8501</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8972</v>
+        <v>0.8501</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8972</v>
+        <v>0.8501</v>
       </c>
       <c r="N20" t="n">
         <v>103</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8378</v>
+        <v>0.8004</v>
       </c>
       <c r="C21" t="n">
-        <v>0.3214</v>
+        <v>0.307</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2428</v>
+        <v>-0.2412</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8378</v>
+        <v>0.8004</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8378</v>
+        <v>0.8004</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8378</v>
+        <v>0.8004</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8378</v>
+        <v>0.8004</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8378</v>
+        <v>0.8004</v>
       </c>
       <c r="N21" t="n">
         <v>103</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7266</v>
+        <v>0.7222</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2787</v>
+        <v>0.277</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2934</v>
+        <v>-0.2768</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7266</v>
+        <v>0.7222</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7266</v>
+        <v>0.7222</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7266</v>
+        <v>0.7222</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7266</v>
+        <v>0.7222</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7266</v>
+        <v>0.7222</v>
       </c>
       <c r="N22" t="n">
-        <v>152</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6849</v>
+        <v>0.7133</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2627</v>
+        <v>0.2736</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3124</v>
+        <v>-0.2808</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6849</v>
+        <v>0.7133</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8911</v>
+        <v>0.944</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2062</v>
+        <v>-0.2307</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8911</v>
+        <v>0.944</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4812</v>
+        <v>0.53</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2062</v>
+        <v>-0.2307</v>
       </c>
       <c r="K23" t="n">
         <v>102</v>
@@ -1495,7 +1495,7 @@
         <v>82</v>
       </c>
       <c r="M23" t="n">
-        <v>0.275</v>
+        <v>0.2993</v>
       </c>
       <c r="N23" t="n">
         <v>184</v>
@@ -1504,139 +1504,139 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2508</v>
+        <v>0.2333</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3266</v>
+        <v>-0.3287</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6536999999999999</v>
+        <v>0.6082</v>
       </c>
       <c r="N24" t="n">
-        <v>103</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.611</v>
+        <v>0.5723</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2344</v>
+        <v>0.2195</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3461</v>
+        <v>-0.3451</v>
       </c>
       <c r="E25" t="n">
-        <v>0.611</v>
+        <v>0.5723</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0883</v>
+        <v>0.5723</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5227000000000001</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0883</v>
+        <v>0.5723</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0477</v>
+        <v>0.5723</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5227000000000001</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="L25" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5704</v>
+        <v>0.5723</v>
       </c>
       <c r="N25" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5855</v>
+        <v>0.5381</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2246</v>
+        <v>0.2064</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3577</v>
+        <v>-0.3607</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5855</v>
+        <v>0.5381</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5855</v>
+        <v>0.078</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.4601</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5855</v>
+        <v>0.078</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5855</v>
+        <v>0.0438</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>0.4601</v>
       </c>
       <c r="K26" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5855</v>
+        <v>0.5039</v>
       </c>
       <c r="N26" t="n">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5172</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2032</v>
+        <v>0.1984</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.3831</v>
+        <v>-0.3702</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5296999999999999</v>
+        <v>0.5172</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9858</v>
+        <v>0.9452</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4561</v>
+        <v>-0.428</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9858</v>
+        <v>0.9452</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5323</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.4561</v>
+        <v>-0.428</v>
       </c>
       <c r="K27" t="n">
         <v>102</v>
@@ -1679,7 +1679,7 @@
         <v>82</v>
       </c>
       <c r="M27" t="n">
-        <v>0.07619999999999999</v>
+        <v>0.1027</v>
       </c>
       <c r="N27" t="n">
         <v>184</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.3572</v>
+        <v>0.3503</v>
       </c>
       <c r="C28" t="n">
-        <v>0.137</v>
+        <v>0.1344</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4616</v>
+        <v>-0.4462</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3572</v>
+        <v>0.3503</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3572</v>
+        <v>0.3503</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3572</v>
+        <v>0.3503</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3572</v>
+        <v>0.3503</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.3572</v>
+        <v>0.3503</v>
       </c>
       <c r="N28" t="n">
         <v>152</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3074</v>
+        <v>0.2813</v>
       </c>
       <c r="C29" t="n">
-        <v>0.1179</v>
+        <v>0.1079</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4843</v>
+        <v>-0.4776</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3074</v>
+        <v>0.2813</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3074</v>
+        <v>0.2813</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3074</v>
+        <v>0.2813</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3074</v>
+        <v>0.2813</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.3074</v>
+        <v>0.2813</v>
       </c>
       <c r="N29" t="n">
         <v>152</v>
@@ -1780,93 +1780,93 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.2116</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0382</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5279</v>
+        <v>-0.5604</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2116</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>1.1885</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.9769</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1885</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6418</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9769</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>51</v>
+        <v>105</v>
       </c>
       <c r="L30" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3351</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>276</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.1799</v>
+        <v>0.0769</v>
       </c>
       <c r="C31" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.0295</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5423</v>
+        <v>-0.5708</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1799</v>
+        <v>0.0769</v>
       </c>
       <c r="F31" t="n">
-        <v>0.1799</v>
+        <v>1.0312</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-0.9543</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1799</v>
+        <v>1.0312</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1799</v>
+        <v>0.579</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-0.9543</v>
       </c>
       <c r="K31" t="n">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="M31" t="n">
-        <v>0.1799</v>
+        <v>-0.3753000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>105</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.0755</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.029</v>
+        <v>-0.0311</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6586</v>
+        <v>-0.6427</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.0755</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0755</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0755</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.0755</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0755</v>
+        <v>-0.08110000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>105</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.078</v>
+        <v>-0.0824</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0299</v>
+        <v>-0.0316</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6597</v>
+        <v>-0.6433</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.078</v>
+        <v>-0.0824</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.078</v>
+        <v>-0.0824</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.078</v>
+        <v>-0.0824</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.078</v>
+        <v>-0.0824</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.078</v>
+        <v>-0.0824</v>
       </c>
       <c r="N33" t="n">
         <v>105</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.319</v>
+        <v>-0.3003</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1224</v>
+        <v>-0.1152</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7694</v>
+        <v>-0.7426</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.319</v>
+        <v>-0.3003</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.319</v>
+        <v>-0.3003</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.319</v>
+        <v>-0.3003</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.319</v>
+        <v>-0.3003</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.319</v>
+        <v>-0.3003</v>
       </c>
       <c r="N34" t="n">
         <v>103</v>
@@ -2010,93 +2010,93 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.3843</v>
+        <v>-0.3569</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1474</v>
+        <v>-0.1369</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7991</v>
+        <v>-0.7684</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.3843</v>
+        <v>-0.3569</v>
       </c>
       <c r="F35" t="n">
-        <v>0.435</v>
+        <v>-0.3569</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8193</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.435</v>
+        <v>-0.3569</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2349</v>
+        <v>-0.3569</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8193</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="L35" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5844</v>
+        <v>-0.3569</v>
       </c>
       <c r="N35" t="n">
-        <v>135</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.4</v>
+        <v>-0.4052</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1534</v>
+        <v>-0.1554</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8063</v>
+        <v>-0.7904</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.4</v>
+        <v>-0.4052</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.4</v>
+        <v>0.4515</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-0.8567</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.4</v>
+        <v>0.4515</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4</v>
+        <v>0.2535</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>-0.8567</v>
       </c>
       <c r="K36" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.4</v>
+        <v>-0.6032</v>
       </c>
       <c r="N36" t="n">
-        <v>87</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.538</v>
+        <v>-0.4806</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2064</v>
+        <v>-0.1844</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8691</v>
+        <v>-0.8247</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.538</v>
+        <v>-0.4806</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.538</v>
+        <v>-0.4806</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.538</v>
+        <v>-0.4806</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.538</v>
+        <v>-0.4806</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.538</v>
+        <v>-0.4806</v>
       </c>
       <c r="N37" t="n">
         <v>87</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.6122</v>
+        <v>-0.6037</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2348</v>
+        <v>-0.2316</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9029</v>
+        <v>-0.8808</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.6122</v>
+        <v>-0.6037</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6122</v>
+        <v>-0.6037</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6122</v>
+        <v>-0.6037</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6122</v>
+        <v>-0.6037</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.6122</v>
+        <v>-0.6037</v>
       </c>
       <c r="N38" t="n">
         <v>105</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1998</v>
+        <v>-1.1787</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.4602</v>
+        <v>-0.4521</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1704</v>
+        <v>-1.1427</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1998</v>
+        <v>-1.1787</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1998</v>
+        <v>-1.1787</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1998</v>
+        <v>-1.1787</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1998</v>
+        <v>-1.1787</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1998</v>
+        <v>-1.1787</v>
       </c>
       <c r="N39" t="n">
         <v>87</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3092</v>
+        <v>-1.302</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.5022</v>
+        <v>-0.4994</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2202</v>
+        <v>-1.1989</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3092</v>
+        <v>-1.302</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3092</v>
+        <v>-1.302</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3092</v>
+        <v>-1.302</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3092</v>
+        <v>-1.302</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3092</v>
+        <v>-1.302</v>
       </c>
       <c r="N40" t="n">
         <v>103</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.7848</v>
+        <v>-1.7169</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.6846</v>
+        <v>-0.6586</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4367</v>
+        <v>-1.3879</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.7848</v>
+        <v>-1.7169</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1969</v>
+        <v>-1.0845</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.5879</v>
+        <v>-0.6324</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1969</v>
+        <v>-1.0845</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6463</v>
+        <v>-0.6089</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.5879</v>
+        <v>-0.6324</v>
       </c>
       <c r="K41" t="n">
         <v>167</v>
@@ -2323,7 +2323,7 @@
         <v>213</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.2342</v>
+        <v>-1.2413</v>
       </c>
       <c r="N41" t="n">
         <v>380</v>
@@ -2429,10 +2429,10 @@
         <v>1.24</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3993</v>
+        <v>0.3969</v>
       </c>
       <c r="J2" t="n">
-        <v>10.3818</v>
+        <v>10.3194</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.203</v>
+        <v>0.1861</v>
       </c>
       <c r="J3" t="n">
-        <v>5.278</v>
+        <v>4.8386</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.98</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.041</v>
+        <v>-0.0317</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.066</v>
+        <v>-0.8242</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.79</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2591</v>
+        <v>-0.2394</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.7366</v>
+        <v>-6.2244</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.72</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3261</v>
+        <v>-0.3095</v>
       </c>
       <c r="J6" t="n">
-        <v>-8.4786</v>
+        <v>-8.047000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.69</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8204</v>
+        <v>0.7514</v>
       </c>
       <c r="J7" t="n">
-        <v>21.3304</v>
+        <v>19.5364</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.17</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2649</v>
+        <v>0.2155</v>
       </c>
       <c r="J8" t="n">
-        <v>6.8874</v>
+        <v>5.603</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.07</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1284</v>
+        <v>0.0983</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3384</v>
+        <v>2.5558</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0175</v>
+        <v>0.0106</v>
       </c>
       <c r="J10" t="n">
-        <v>0.455</v>
+        <v>0.2756</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.9</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1609</v>
+        <v>-0.1412</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.1834</v>
+        <v>-3.6712</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.63</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3916</v>
+        <v>1.4295</v>
       </c>
       <c r="J12" t="n">
-        <v>40.3564</v>
+        <v>41.4555</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8227</v>
+        <v>0.7986</v>
       </c>
       <c r="J13" t="n">
-        <v>23.8583</v>
+        <v>23.1594</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1767</v>
+        <v>0.1498</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1243</v>
+        <v>4.3442</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.89</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.399</v>
+        <v>-0.357</v>
       </c>
       <c r="J15" t="n">
-        <v>-11.571</v>
+        <v>-10.353</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.399</v>
+        <v>-0.357</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.571</v>
+        <v>-10.353</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.47</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8758</v>
+        <v>0.8335</v>
       </c>
       <c r="J17" t="n">
-        <v>25.3982</v>
+        <v>24.1715</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.98</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0396</v>
+        <v>-0.0308</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1484</v>
+        <v>-0.8932</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2374</v>
+        <v>-0.2173</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.8846</v>
+        <v>-6.3017</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.75</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2959</v>
+        <v>-0.2776</v>
       </c>
       <c r="J20" t="n">
-        <v>-8.581099999999999</v>
+        <v>-8.0504</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.72</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3242</v>
+        <v>-0.3074</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.4018</v>
+        <v>-8.9146</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>0.99</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0052</v>
+        <v>-0.0007</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1352</v>
+        <v>-0.0182</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>0.92</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1076</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.7976</v>
+        <v>-2.4258</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.82</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2163</v>
+        <v>-0.1986</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.6238</v>
+        <v>-5.1636</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.73</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.3015</v>
+        <v>-0.2842</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.839</v>
+        <v>-7.3892</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4019</v>
+        <v>-0.3905</v>
       </c>
       <c r="J26" t="n">
-        <v>-10.4494</v>
+        <v>-10.153</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.65</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.6815</v>
       </c>
       <c r="J27" t="n">
-        <v>19.591</v>
+        <v>17.719</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.34</v>
       </c>
       <c r="I28" t="n">
-        <v>0.4458</v>
+        <v>0.3837</v>
       </c>
       <c r="J28" t="n">
-        <v>11.5908</v>
+        <v>9.9762</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.28</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3824</v>
+        <v>0.3251</v>
       </c>
       <c r="J29" t="n">
-        <v>9.942399999999999</v>
+        <v>8.4526</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>1.27</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3713</v>
+        <v>0.3149</v>
       </c>
       <c r="J30" t="n">
-        <v>9.6538</v>
+        <v>8.1874</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>1.09</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1444</v>
+        <v>0.1121</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7544</v>
+        <v>2.9146</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.89</v>
       </c>
       <c r="I32" t="n">
-        <v>1.7537</v>
+        <v>1.7978</v>
       </c>
       <c r="J32" t="n">
-        <v>47.3499</v>
+        <v>48.5406</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.39</v>
       </c>
       <c r="I33" t="n">
-        <v>0.931</v>
+        <v>0.9165</v>
       </c>
       <c r="J33" t="n">
-        <v>25.137</v>
+        <v>24.7455</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.36</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.8532</v>
       </c>
       <c r="J34" t="n">
-        <v>23.5575</v>
+        <v>23.0364</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4827</v>
+        <v>-0.4427</v>
       </c>
       <c r="J35" t="n">
-        <v>-13.0329</v>
+        <v>-11.9529</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.5</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.2454</v>
+        <v>-1.2836</v>
       </c>
       <c r="J36" t="n">
-        <v>-33.6258</v>
+        <v>-34.6572</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.24</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5169</v>
+        <v>0.4592</v>
       </c>
       <c r="J37" t="n">
-        <v>13.9563</v>
+        <v>12.3984</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.92</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1191</v>
+        <v>-0.1018</v>
       </c>
       <c r="J38" t="n">
-        <v>-3.2157</v>
+        <v>-2.7486</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.89</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1533</v>
+        <v>-0.1341</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.1391</v>
+        <v>-3.6207</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.88</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.1642</v>
+        <v>-0.1447</v>
       </c>
       <c r="J40" t="n">
-        <v>-4.4334</v>
+        <v>-3.9069</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.78</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2666</v>
+        <v>-0.2472</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.1982</v>
+        <v>-6.6744</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.44</v>
       </c>
       <c r="I42" t="n">
-        <v>1.0164</v>
+        <v>1.0108</v>
       </c>
       <c r="J42" t="n">
-        <v>35.574</v>
+        <v>35.378</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.41</v>
       </c>
       <c r="I43" t="n">
-        <v>0.9597</v>
+        <v>0.9488</v>
       </c>
       <c r="J43" t="n">
-        <v>33.5895</v>
+        <v>33.208</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.34</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8247</v>
+        <v>0.8036</v>
       </c>
       <c r="J44" t="n">
-        <v>28.8645</v>
+        <v>28.126</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1306</v>
+        <v>0.1071</v>
       </c>
       <c r="J45" t="n">
-        <v>4.571</v>
+        <v>3.7485</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.98</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1422</v>
+        <v>-0.1154</v>
       </c>
       <c r="J46" t="n">
-        <v>-4.977</v>
+        <v>-4.039</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.23</v>
       </c>
       <c r="I47" t="n">
-        <v>0.507</v>
+        <v>0.4502</v>
       </c>
       <c r="J47" t="n">
-        <v>17.745</v>
+        <v>15.757</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.11</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2896</v>
+        <v>0.24</v>
       </c>
       <c r="J48" t="n">
-        <v>10.136</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>0.85</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1942</v>
+        <v>-0.1743</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.797</v>
+        <v>-6.1005</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.235</v>
+        <v>-0.215</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.225</v>
+        <v>-7.525</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4302</v>
+        <v>-0.4223</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.057</v>
+        <v>-14.7805</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2446</v>
+        <v>0.2299</v>
       </c>
       <c r="J52" t="n">
-        <v>7.338</v>
+        <v>6.897</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.99</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.0181</v>
+        <v>-0.0133</v>
       </c>
       <c r="J53" t="n">
-        <v>-0.543</v>
+        <v>-0.399</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.98</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.036</v>
+        <v>-0.0281</v>
       </c>
       <c r="J54" t="n">
-        <v>-1.08</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2338</v>
+        <v>-0.2139</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.014</v>
+        <v>-6.417</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.64</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3936</v>
+        <v>-0.3819</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.808</v>
+        <v>-11.457</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.92</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8838</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>26.514</v>
+        <v>24.996</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.12</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2011</v>
+        <v>0.1599</v>
       </c>
       <c r="J58" t="n">
-        <v>6.033</v>
+        <v>4.797</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.01</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0179</v>
+        <v>0.0109</v>
       </c>
       <c r="J59" t="n">
-        <v>0.537</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1606</v>
+        <v>-0.1408</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.818</v>
+        <v>-4.224</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.87</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1939</v>
+        <v>-0.1739</v>
       </c>
       <c r="J61" t="n">
-        <v>-5.817</v>
+        <v>-5.217</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.78</v>
       </c>
       <c r="I62" t="n">
-        <v>1.2904</v>
+        <v>1.2923</v>
       </c>
       <c r="J62" t="n">
-        <v>30.9696</v>
+        <v>31.0152</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.6</v>
       </c>
       <c r="I63" t="n">
-        <v>1.0627</v>
+        <v>1.0528</v>
       </c>
       <c r="J63" t="n">
-        <v>25.5048</v>
+        <v>25.2672</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.39</v>
       </c>
       <c r="I64" t="n">
-        <v>0.783</v>
+        <v>0.7714</v>
       </c>
       <c r="J64" t="n">
-        <v>18.792</v>
+        <v>18.5136</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.15</v>
       </c>
       <c r="I65" t="n">
-        <v>0.4113</v>
+        <v>0.3802</v>
       </c>
       <c r="J65" t="n">
-        <v>9.8712</v>
+        <v>9.1248</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.79</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6699000000000001</v>
+        <v>-0.643</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.0776</v>
+        <v>-15.432</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.06</v>
       </c>
       <c r="I67" t="n">
-        <v>0.2128</v>
+        <v>0.1734</v>
       </c>
       <c r="J67" t="n">
-        <v>5.1072</v>
+        <v>4.1616</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0.0344</v>
+        <v>0.0286</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8256</v>
+        <v>0.6864</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.86</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1764</v>
+        <v>-0.1595</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.2336</v>
+        <v>-3.828</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.62</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4025</v>
+        <v>-0.3913</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.66</v>
+        <v>-9.3912</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.57</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4469</v>
+        <v>-0.4399</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.7256</v>
+        <v>-10.5576</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.36</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7677</v>
+        <v>0.7518</v>
       </c>
       <c r="J72" t="n">
-        <v>21.4956</v>
+        <v>21.0504</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.19</v>
       </c>
       <c r="I73" t="n">
-        <v>0.5052</v>
+        <v>0.4907</v>
       </c>
       <c r="J73" t="n">
-        <v>14.1456</v>
+        <v>13.7396</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.18</v>
       </c>
       <c r="I74" t="n">
-        <v>0.4888</v>
+        <v>0.4694</v>
       </c>
       <c r="J74" t="n">
-        <v>13.6864</v>
+        <v>13.1432</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.08</v>
       </c>
       <c r="I75" t="n">
-        <v>0.2642</v>
+        <v>0.232</v>
       </c>
       <c r="J75" t="n">
-        <v>7.3976</v>
+        <v>6.496</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.96</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.1971</v>
+        <v>-0.1624</v>
       </c>
       <c r="J76" t="n">
-        <v>-5.5188</v>
+        <v>-4.5472</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.17</v>
       </c>
       <c r="I77" t="n">
-        <v>0.3902</v>
+        <v>0.3345</v>
       </c>
       <c r="J77" t="n">
-        <v>10.9256</v>
+        <v>9.366</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.99</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.0233</v>
+        <v>-0.0172</v>
       </c>
       <c r="J78" t="n">
-        <v>-0.6524</v>
+        <v>-0.4816</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.98</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.0409</v>
+        <v>-0.0316</v>
       </c>
       <c r="J79" t="n">
-        <v>-1.1452</v>
+        <v>-0.8848</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.93</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1087</v>
+        <v>-0.0917</v>
       </c>
       <c r="J80" t="n">
-        <v>-3.0436</v>
+        <v>-2.5676</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.75</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2976</v>
+        <v>-0.2794</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.332800000000001</v>
+        <v>-7.8232</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>0.93</v>
       </c>
       <c r="I82" t="n">
-        <v>-0.0541</v>
+        <v>-0.0336</v>
       </c>
       <c r="J82" t="n">
-        <v>-1.082</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.91</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0806</v>
+        <v>-0.0604</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.612</v>
+        <v>-1.208</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.62</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.3802</v>
+        <v>-0.3704</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.604</v>
+        <v>-7.408</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.47</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5115</v>
+        <v>-0.5109</v>
       </c>
       <c r="J85" t="n">
-        <v>-10.23</v>
+        <v>-10.218</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.24</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7126</v>
+        <v>-0.7462</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.252</v>
+        <v>-14.924</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.95</v>
       </c>
       <c r="I87" t="n">
-        <v>1.4549</v>
+        <v>1.4686</v>
       </c>
       <c r="J87" t="n">
-        <v>29.098</v>
+        <v>29.372</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.79</v>
       </c>
       <c r="I88" t="n">
-        <v>1.2669</v>
+        <v>1.2687</v>
       </c>
       <c r="J88" t="n">
-        <v>25.338</v>
+        <v>25.374</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.48</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8872</v>
+        <v>0.881</v>
       </c>
       <c r="J89" t="n">
-        <v>17.744</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.32</v>
       </c>
       <c r="I90" t="n">
-        <v>0.6669</v>
+        <v>0.6629</v>
       </c>
       <c r="J90" t="n">
-        <v>13.338</v>
+        <v>13.258</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.18</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4471</v>
+        <v>0.4208</v>
       </c>
       <c r="J91" t="n">
-        <v>8.942</v>
+        <v>8.416</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.36</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4725</v>
+        <v>0.4169</v>
       </c>
       <c r="J92" t="n">
-        <v>11.34</v>
+        <v>10.0056</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.26</v>
       </c>
       <c r="I93" t="n">
-        <v>0.3726</v>
+        <v>0.3121</v>
       </c>
       <c r="J93" t="n">
-        <v>8.942399999999999</v>
+        <v>7.4904</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.188</v>
+        <v>0.1485</v>
       </c>
       <c r="J94" t="n">
-        <v>4.512</v>
+        <v>3.564</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.1</v>
       </c>
       <c r="I95" t="n">
-        <v>0.174</v>
+        <v>0.1365</v>
       </c>
       <c r="J95" t="n">
-        <v>4.176</v>
+        <v>3.276</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.95</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J96" t="n">
-        <v>-2.3664</v>
+        <v>-1.9584</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.25</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4233</v>
+        <v>0.4269</v>
       </c>
       <c r="J97" t="n">
-        <v>10.1592</v>
+        <v>10.2456</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0936</v>
+        <v>-0.079</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.2464</v>
+        <v>-1.896</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.91</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.129</v>
+        <v>-0.1117</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.096</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2346</v>
+        <v>-0.2146</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.6304</v>
+        <v>-5.1504</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.67</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3673</v>
+        <v>-0.3534</v>
       </c>
       <c r="J101" t="n">
-        <v>-8.815200000000001</v>
+        <v>-8.4816</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.16</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4293</v>
+        <v>0.384</v>
       </c>
       <c r="J102" t="n">
-        <v>11.1618</v>
+        <v>9.984</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>0.98</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.0188</v>
+        <v>-0.0112</v>
       </c>
       <c r="J103" t="n">
-        <v>-0.4888</v>
+        <v>-0.2912</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3356</v>
+        <v>-0.32</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.7256</v>
+        <v>-8.32</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.61</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.4079</v>
+        <v>-0.397</v>
       </c>
       <c r="J105" t="n">
-        <v>-10.6054</v>
+        <v>-10.322</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.51</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4958</v>
+        <v>-0.4943</v>
       </c>
       <c r="J106" t="n">
-        <v>-12.8908</v>
+        <v>-12.8518</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.6</v>
       </c>
       <c r="I107" t="n">
-        <v>1.0562</v>
+        <v>1.0467</v>
       </c>
       <c r="J107" t="n">
-        <v>27.4612</v>
+        <v>27.2142</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.45</v>
       </c>
       <c r="I108" t="n">
-        <v>0.8601</v>
+        <v>0.8488</v>
       </c>
       <c r="J108" t="n">
-        <v>22.3626</v>
+        <v>22.0688</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.41</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8066</v>
+        <v>0.796</v>
       </c>
       <c r="J109" t="n">
-        <v>20.9716</v>
+        <v>20.696</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>1.33</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6973</v>
+        <v>0.6895</v>
       </c>
       <c r="J110" t="n">
-        <v>18.1298</v>
+        <v>17.927</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>1.12</v>
       </c>
       <c r="I111" t="n">
-        <v>0.3323</v>
+        <v>0.3002</v>
       </c>
       <c r="J111" t="n">
-        <v>8.639799999999999</v>
+        <v>7.8052</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.88</v>
       </c>
       <c r="I112" t="n">
-        <v>1.5521</v>
+        <v>1.5879</v>
       </c>
       <c r="J112" t="n">
-        <v>34.1462</v>
+        <v>34.9338</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.37</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8642</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>19.0124</v>
+        <v>18.7506</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.28</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6901</v>
+        <v>0.6685</v>
       </c>
       <c r="J114" t="n">
-        <v>15.1822</v>
+        <v>14.707</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5209</v>
+        <v>0.4921</v>
       </c>
       <c r="J115" t="n">
-        <v>11.4598</v>
+        <v>10.8262</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>1.16</v>
       </c>
       <c r="I116" t="n">
-        <v>0.4298</v>
+        <v>0.3987</v>
       </c>
       <c r="J116" t="n">
-        <v>9.4556</v>
+        <v>8.7714</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0593</v>
+        <v>-0.0469</v>
       </c>
       <c r="J117" t="n">
-        <v>-1.3046</v>
+        <v>-1.0318</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.85</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1797</v>
+        <v>-0.1639</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.9534</v>
+        <v>-3.6058</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2008</v>
+        <v>-0.1849</v>
       </c>
       <c r="J119" t="n">
-        <v>-4.4176</v>
+        <v>-4.0678</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.59</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4224</v>
+        <v>-0.4128</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.2928</v>
+        <v>-9.0816</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.59</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4224</v>
+        <v>-0.4128</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.2928</v>
+        <v>-9.0816</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.59</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2349</v>
+        <v>1.2523</v>
       </c>
       <c r="J122" t="n">
-        <v>35.8121</v>
+        <v>36.3167</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.32</v>
       </c>
       <c r="I123" t="n">
-        <v>0.8006</v>
+        <v>0.7752</v>
       </c>
       <c r="J123" t="n">
-        <v>23.2174</v>
+        <v>22.4808</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.0275</v>
+        <v>-0.022</v>
       </c>
       <c r="J124" t="n">
-        <v>-0.7975</v>
+        <v>-0.638</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.0664</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.5346</v>
+        <v>-1.9256</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.291</v>
+        <v>-0.2511</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.439</v>
+        <v>-7.2819</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2567</v>
+        <v>0.2095</v>
       </c>
       <c r="J127" t="n">
-        <v>7.4443</v>
+        <v>6.0755</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.05</v>
       </c>
       <c r="I128" t="n">
-        <v>0.1513</v>
+        <v>0.1163</v>
       </c>
       <c r="J128" t="n">
-        <v>4.3877</v>
+        <v>3.3727</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.01</v>
       </c>
       <c r="I129" t="n">
-        <v>0.0458</v>
+        <v>0.0307</v>
       </c>
       <c r="J129" t="n">
-        <v>1.3282</v>
+        <v>0.8903</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.92</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1218</v>
+        <v>-0.1037</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.5322</v>
+        <v>-3.0073</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2404</v>
+        <v>-0.2202</v>
       </c>
       <c r="J131" t="n">
-        <v>-6.9716</v>
+        <v>-6.3858</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.31</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6391</v>
+        <v>0.5847</v>
       </c>
       <c r="J132" t="n">
-        <v>17.8948</v>
+        <v>16.3716</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.06</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1854</v>
+        <v>0.1456</v>
       </c>
       <c r="J133" t="n">
-        <v>5.1912</v>
+        <v>4.0768</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.91</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1292</v>
+        <v>-0.1118</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.6176</v>
+        <v>-3.1304</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.68</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3586</v>
+        <v>-0.3441</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.0408</v>
+        <v>-9.6348</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.64</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3947</v>
+        <v>-0.3833</v>
       </c>
       <c r="J136" t="n">
-        <v>-11.0516</v>
+        <v>-10.7324</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.76</v>
       </c>
       <c r="I137" t="n">
-        <v>1.4219</v>
+        <v>1.4486</v>
       </c>
       <c r="J137" t="n">
-        <v>39.8132</v>
+        <v>40.5608</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.26</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6595</v>
+        <v>0.6334</v>
       </c>
       <c r="J138" t="n">
-        <v>18.466</v>
+        <v>17.7352</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.2</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5322</v>
+        <v>0.5022</v>
       </c>
       <c r="J139" t="n">
-        <v>14.9016</v>
+        <v>14.0616</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.19</v>
       </c>
       <c r="I140" t="n">
-        <v>0.51</v>
+        <v>0.4795</v>
       </c>
       <c r="J140" t="n">
-        <v>14.28</v>
+        <v>13.426</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.1</v>
       </c>
       <c r="I141" t="n">
-        <v>0.2936</v>
+        <v>0.2621</v>
       </c>
       <c r="J141" t="n">
-        <v>8.220800000000001</v>
+        <v>7.3388</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.25</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5851</v>
+        <v>0.5384</v>
       </c>
       <c r="J142" t="n">
-        <v>16.9679</v>
+        <v>15.6136</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.85</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1857</v>
+        <v>-0.1689</v>
       </c>
       <c r="J143" t="n">
-        <v>-5.3853</v>
+        <v>-4.8981</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.72</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3102</v>
+        <v>-0.2933</v>
       </c>
       <c r="J144" t="n">
-        <v>-8.995799999999999</v>
+        <v>-8.505699999999999</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.64</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3833</v>
+        <v>-0.3704</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.1157</v>
+        <v>-10.7416</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.59</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4279</v>
+        <v>-0.4189</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.4091</v>
+        <v>-12.1481</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.4</v>
       </c>
       <c r="I147" t="n">
-        <v>0.9342</v>
+        <v>0.9229000000000001</v>
       </c>
       <c r="J147" t="n">
-        <v>27.0918</v>
+        <v>26.7641</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.36</v>
       </c>
       <c r="I148" t="n">
-        <v>0.8586</v>
+        <v>0.8409</v>
       </c>
       <c r="J148" t="n">
-        <v>24.8994</v>
+        <v>24.3861</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.34</v>
       </c>
       <c r="I149" t="n">
-        <v>0.82</v>
+        <v>0.7998</v>
       </c>
       <c r="J149" t="n">
-        <v>23.78</v>
+        <v>23.1942</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.14</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3991</v>
+        <v>0.3666</v>
       </c>
       <c r="J150" t="n">
-        <v>11.5739</v>
+        <v>10.6314</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>1.11</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3247</v>
+        <v>0.2926</v>
       </c>
       <c r="J151" t="n">
-        <v>9.4163</v>
+        <v>8.4854</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.29</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6039</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>21.1365</v>
+        <v>19.1765</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.95</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0679</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.856</v>
+        <v>-2.3765</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.9</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.141</v>
+        <v>-0.1227</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.935</v>
+        <v>-4.2945</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.86</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.1845</v>
+        <v>-0.1646</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.4575</v>
+        <v>-5.761</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.64</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3955</v>
+        <v>-0.3842</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.8425</v>
+        <v>-13.447</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.26</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6725</v>
+        <v>0.6412</v>
       </c>
       <c r="J157" t="n">
-        <v>23.5375</v>
+        <v>22.442</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.25</v>
       </c>
       <c r="I158" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6196</v>
       </c>
       <c r="J158" t="n">
-        <v>22.8095</v>
+        <v>21.686</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.18</v>
       </c>
       <c r="I159" t="n">
-        <v>0.5028</v>
+        <v>0.4678</v>
       </c>
       <c r="J159" t="n">
-        <v>17.598</v>
+        <v>16.373</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.16</v>
       </c>
       <c r="I160" t="n">
-        <v>0.4579</v>
+        <v>0.4228</v>
       </c>
       <c r="J160" t="n">
-        <v>16.0265</v>
+        <v>14.798</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.11</v>
       </c>
       <c r="I161" t="n">
-        <v>0.3373</v>
+        <v>0.3036</v>
       </c>
       <c r="J161" t="n">
-        <v>11.8055</v>
+        <v>10.626</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.01</v>
       </c>
       <c r="I162" t="n">
-        <v>0.059</v>
+        <v>0.0407</v>
       </c>
       <c r="J162" t="n">
-        <v>1.534</v>
+        <v>1.0582</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.97</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.0512</v>
+        <v>-0.0412</v>
       </c>
       <c r="J163" t="n">
-        <v>-1.3312</v>
+        <v>-1.0712</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1049</v>
+        <v>-0.0897</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.7274</v>
+        <v>-2.3322</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.8</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.2432</v>
+        <v>-0.2234</v>
       </c>
       <c r="J165" t="n">
-        <v>-6.3232</v>
+        <v>-5.8084</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.8</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2432</v>
+        <v>-0.2234</v>
       </c>
       <c r="J166" t="n">
-        <v>-6.3232</v>
+        <v>-5.8084</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.54</v>
       </c>
       <c r="I167" t="n">
-        <v>1.1502</v>
+        <v>1.1632</v>
       </c>
       <c r="J167" t="n">
-        <v>29.9052</v>
+        <v>30.2432</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.4</v>
       </c>
       <c r="I168" t="n">
-        <v>0.9401</v>
+        <v>0.9285</v>
       </c>
       <c r="J168" t="n">
-        <v>24.4426</v>
+        <v>24.141</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.19</v>
       </c>
       <c r="I169" t="n">
-        <v>0.519</v>
+        <v>0.4865</v>
       </c>
       <c r="J169" t="n">
-        <v>13.494</v>
+        <v>12.649</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.07</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2219</v>
+        <v>0.1927</v>
       </c>
       <c r="J170" t="n">
-        <v>5.7694</v>
+        <v>5.0102</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>1</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.0405</v>
+        <v>-0.0351</v>
       </c>
       <c r="J171" t="n">
-        <v>-1.053</v>
+        <v>-0.9126</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.71</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8205</v>
+        <v>0.7497</v>
       </c>
       <c r="J172" t="n">
-        <v>20.5125</v>
+        <v>18.7425</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.34</v>
       </c>
       <c r="I173" t="n">
-        <v>0.4504</v>
+        <v>0.3863</v>
       </c>
       <c r="J173" t="n">
-        <v>11.26</v>
+        <v>9.657500000000001</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.3</v>
       </c>
       <c r="I174" t="n">
-        <v>0.4074</v>
+        <v>0.3465</v>
       </c>
       <c r="J174" t="n">
-        <v>10.185</v>
+        <v>8.6625</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.13</v>
       </c>
       <c r="I175" t="n">
-        <v>0.2061</v>
+        <v>0.1656</v>
       </c>
       <c r="J175" t="n">
-        <v>5.1525</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.84</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.2329</v>
+        <v>-0.2146</v>
       </c>
       <c r="J176" t="n">
-        <v>-5.8225</v>
+        <v>-5.365</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.23</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4097</v>
+        <v>0.4123</v>
       </c>
       <c r="J177" t="n">
-        <v>10.2425</v>
+        <v>10.3075</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>0.93</v>
       </c>
       <c r="I178" t="n">
-        <v>-0.1023</v>
+        <v>-0.0878</v>
       </c>
       <c r="J178" t="n">
-        <v>-2.5575</v>
+        <v>-2.195</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.79</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2502</v>
+        <v>-0.231</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.255</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.73</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3076</v>
+        <v>-0.29</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.69</v>
+        <v>-7.25</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3447</v>
+        <v>-0.3292</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.6175</v>
+        <v>-8.23</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.11</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2837</v>
+        <v>0.2342</v>
       </c>
       <c r="J182" t="n">
-        <v>7.9436</v>
+        <v>6.5576</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.01</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0509</v>
+        <v>0.0342</v>
       </c>
       <c r="J183" t="n">
-        <v>1.4252</v>
+        <v>0.9576</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1423</v>
+        <v>-0.1236</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.9844</v>
+        <v>-3.4608</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.87</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1752</v>
+        <v>-0.1553</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.9056</v>
+        <v>-4.3484</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.83</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.217</v>
+        <v>-0.1967</v>
       </c>
       <c r="J186" t="n">
-        <v>-6.076</v>
+        <v>-5.5076</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.56</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1922</v>
+        <v>1.2074</v>
       </c>
       <c r="J187" t="n">
-        <v>33.3816</v>
+        <v>33.8072</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.41</v>
       </c>
       <c r="I188" t="n">
-        <v>0.973</v>
+        <v>0.9651</v>
       </c>
       <c r="J188" t="n">
-        <v>27.244</v>
+        <v>27.0228</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.31</v>
       </c>
       <c r="I189" t="n">
-        <v>0.7785</v>
+        <v>0.7519</v>
       </c>
       <c r="J189" t="n">
-        <v>21.798</v>
+        <v>21.0532</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.93</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2925</v>
+        <v>-0.2527</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.19</v>
+        <v>-7.0756</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.66</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.9244</v>
+        <v>-0.9164</v>
       </c>
       <c r="J191" t="n">
-        <v>-25.8832</v>
+        <v>-25.6592</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.79</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1915</v>
+        <v>1.181</v>
       </c>
       <c r="J192" t="n">
-        <v>34.5535</v>
+        <v>34.249</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.31</v>
       </c>
       <c r="I193" t="n">
-        <v>0.5881</v>
+        <v>0.5283</v>
       </c>
       <c r="J193" t="n">
-        <v>17.0549</v>
+        <v>15.3207</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.92</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.1321</v>
+        <v>-0.1129</v>
       </c>
       <c r="J194" t="n">
-        <v>-3.8309</v>
+        <v>-3.2741</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.77</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.2905</v>
+        <v>-0.2728</v>
       </c>
       <c r="J195" t="n">
-        <v>-8.4245</v>
+        <v>-7.9112</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.72</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.3377</v>
+        <v>-0.3231</v>
       </c>
       <c r="J196" t="n">
-        <v>-9.7933</v>
+        <v>-9.369899999999999</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.19</v>
       </c>
       <c r="I197" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.528</v>
       </c>
       <c r="J197" t="n">
-        <v>16.472</v>
+        <v>15.312</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.16</v>
       </c>
       <c r="I198" t="n">
-        <v>0.4967</v>
+        <v>0.4545</v>
       </c>
       <c r="J198" t="n">
-        <v>14.4043</v>
+        <v>13.1805</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.98</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0978</v>
+        <v>-0.0756</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.8362</v>
+        <v>-2.1924</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.92</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2854</v>
+        <v>-0.2458</v>
       </c>
       <c r="J200" t="n">
-        <v>-8.2766</v>
+        <v>-7.1282</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.828</v>
+        <v>-0.8048999999999999</v>
       </c>
       <c r="J201" t="n">
-        <v>-24.012</v>
+        <v>-23.3421</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.43</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8354</v>
+        <v>0.7943</v>
       </c>
       <c r="J202" t="n">
-        <v>20.885</v>
+        <v>19.8575</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.82</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2231</v>
+        <v>-0.2032</v>
       </c>
       <c r="J203" t="n">
-        <v>-5.5775</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.8</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.243</v>
+        <v>-0.2233</v>
       </c>
       <c r="J204" t="n">
-        <v>-6.075</v>
+        <v>-5.5825</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.76</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2818</v>
+        <v>-0.2631</v>
       </c>
       <c r="J205" t="n">
-        <v>-7.045</v>
+        <v>-6.5775</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3474</v>
+        <v>-0.332</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.685</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.49</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0805</v>
+        <v>1.0902</v>
       </c>
       <c r="J207" t="n">
-        <v>27.0125</v>
+        <v>27.255</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.37</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8815</v>
+        <v>0.8646</v>
       </c>
       <c r="J208" t="n">
-        <v>22.0375</v>
+        <v>21.615</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.21</v>
       </c>
       <c r="I209" t="n">
-        <v>0.5613</v>
+        <v>0.53</v>
       </c>
       <c r="J209" t="n">
-        <v>14.0325</v>
+        <v>13.25</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.2</v>
       </c>
       <c r="I210" t="n">
-        <v>0.5396</v>
+        <v>0.5079</v>
       </c>
       <c r="J210" t="n">
-        <v>13.49</v>
+        <v>12.6975</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.98</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.1435</v>
+        <v>-0.1169</v>
       </c>
       <c r="J211" t="n">
-        <v>-3.5875</v>
+        <v>-2.9225</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>0.83</v>
       </c>
       <c r="I212" t="n">
-        <v>-0.1948</v>
+        <v>-0.1794</v>
       </c>
       <c r="J212" t="n">
-        <v>-4.4804</v>
+        <v>-4.1262</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>0.82</v>
       </c>
       <c r="I213" t="n">
-        <v>-0.2054</v>
+        <v>-0.19</v>
       </c>
       <c r="J213" t="n">
-        <v>-4.7242</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.68</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.3371</v>
+        <v>-0.323</v>
       </c>
       <c r="J214" t="n">
-        <v>-7.7533</v>
+        <v>-7.429</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.64</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3729</v>
+        <v>-0.3602</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.576700000000001</v>
+        <v>-8.284599999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.64</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3729</v>
+        <v>-0.3602</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.576700000000001</v>
+        <v>-8.284599999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.63</v>
       </c>
       <c r="I217" t="n">
-        <v>1.2395</v>
+        <v>1.257</v>
       </c>
       <c r="J217" t="n">
-        <v>28.5085</v>
+        <v>28.911</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.5</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0718</v>
+        <v>1.0841</v>
       </c>
       <c r="J218" t="n">
-        <v>24.6514</v>
+        <v>24.9343</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.43</v>
       </c>
       <c r="I219" t="n">
-        <v>0.968</v>
+        <v>0.9668</v>
       </c>
       <c r="J219" t="n">
-        <v>22.264</v>
+        <v>22.2364</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.27</v>
       </c>
       <c r="I220" t="n">
-        <v>0.6672</v>
+        <v>0.645</v>
       </c>
       <c r="J220" t="n">
-        <v>15.3456</v>
+        <v>14.835</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>1.15</v>
       </c>
       <c r="I221" t="n">
-        <v>0.4035</v>
+        <v>0.3719</v>
       </c>
       <c r="J221" t="n">
-        <v>9.2805</v>
+        <v>8.553699999999999</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.34</v>
       </c>
       <c r="I222" t="n">
-        <v>0.8694</v>
+        <v>0.8487</v>
       </c>
       <c r="J222" t="n">
-        <v>34.776</v>
+        <v>33.948</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.22</v>
       </c>
       <c r="I223" t="n">
-        <v>0.6137</v>
+        <v>0.5758</v>
       </c>
       <c r="J223" t="n">
-        <v>24.548</v>
+        <v>23.032</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.05</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1912</v>
+        <v>0.1607</v>
       </c>
       <c r="J224" t="n">
-        <v>7.648</v>
+        <v>6.428</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2429</v>
+        <v>-0.2044</v>
       </c>
       <c r="J225" t="n">
-        <v>-9.715999999999999</v>
+        <v>-8.176</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.78</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6466</v>
+        <v>-0.6111</v>
       </c>
       <c r="J226" t="n">
-        <v>-25.864</v>
+        <v>-24.444</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.36</v>
       </c>
       <c r="I227" t="n">
-        <v>0.6806</v>
+        <v>0.6226</v>
       </c>
       <c r="J227" t="n">
-        <v>27.224</v>
+        <v>24.904</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.1</v>
       </c>
       <c r="I228" t="n">
-        <v>0.2469</v>
+        <v>0.2016</v>
       </c>
       <c r="J228" t="n">
-        <v>9.875999999999999</v>
+        <v>8.064</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.09</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2273</v>
+        <v>0.1841</v>
       </c>
       <c r="J229" t="n">
-        <v>9.092000000000001</v>
+        <v>7.364</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.84</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2149</v>
+        <v>-0.1944</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.596</v>
+        <v>-7.776</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.78</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.2751</v>
+        <v>-0.2562</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.004</v>
+        <v>-10.248</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.22</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6091</v>
+        <v>0.5714</v>
       </c>
       <c r="J232" t="n">
-        <v>15.8366</v>
+        <v>14.8564</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.19</v>
       </c>
       <c r="I233" t="n">
-        <v>0.5419</v>
+        <v>0.5022</v>
       </c>
       <c r="J233" t="n">
-        <v>14.0894</v>
+        <v>13.0572</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.12</v>
       </c>
       <c r="I234" t="n">
-        <v>0.3762</v>
+        <v>0.3366</v>
       </c>
       <c r="J234" t="n">
-        <v>9.7812</v>
+        <v>8.7516</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.99</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0725</v>
+        <v>-0.0527</v>
       </c>
       <c r="J235" t="n">
-        <v>-1.885</v>
+        <v>-1.3702</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.9</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.3586</v>
+        <v>-0.316</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.323600000000001</v>
+        <v>-8.215999999999999</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.47</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8749</v>
+        <v>0.8324</v>
       </c>
       <c r="J237" t="n">
-        <v>22.7474</v>
+        <v>21.6424</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.15</v>
       </c>
       <c r="I238" t="n">
-        <v>0.3582</v>
+        <v>0.3041</v>
       </c>
       <c r="J238" t="n">
-        <v>9.3132</v>
+        <v>7.9066</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.89</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1538</v>
+        <v>-0.1345</v>
       </c>
       <c r="J239" t="n">
-        <v>-3.9988</v>
+        <v>-3.497</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.78</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2672</v>
+        <v>-0.2478</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.9472</v>
+        <v>-6.4428</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.45</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5611</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.5886</v>
+        <v>-14.8486</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.13</v>
       </c>
       <c r="I242" t="n">
-        <v>0.3339</v>
+        <v>0.282</v>
       </c>
       <c r="J242" t="n">
-        <v>9.3492</v>
+        <v>7.896</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>0.93</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.1047</v>
+        <v>-0.0896</v>
       </c>
       <c r="J243" t="n">
-        <v>-2.9316</v>
+        <v>-2.5088</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>0.91</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.1283</v>
+        <v>-0.1114</v>
       </c>
       <c r="J244" t="n">
-        <v>-3.5924</v>
+        <v>-3.1192</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.233</v>
+        <v>-0.2133</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.524</v>
+        <v>-5.9724</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.72</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3196</v>
+        <v>-0.3025</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.9488</v>
+        <v>-8.470000000000001</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.4</v>
       </c>
       <c r="I247" t="n">
-        <v>0.9634</v>
+        <v>0.9538</v>
       </c>
       <c r="J247" t="n">
-        <v>26.9752</v>
+        <v>26.7064</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>1.33</v>
       </c>
       <c r="I248" t="n">
-        <v>0.8267</v>
+        <v>0.8026</v>
       </c>
       <c r="J248" t="n">
-        <v>23.1476</v>
+        <v>22.4728</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>1.07</v>
       </c>
       <c r="I249" t="n">
-        <v>0.2383</v>
+        <v>0.2071</v>
       </c>
       <c r="J249" t="n">
-        <v>6.6724</v>
+        <v>5.7988</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.98</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1245</v>
+        <v>-0.09719999999999999</v>
       </c>
       <c r="J250" t="n">
-        <v>-3.486</v>
+        <v>-2.7216</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.93</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.2866</v>
+        <v>-0.2465</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.024800000000001</v>
+        <v>-6.902</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>0.93</v>
       </c>
       <c r="I252" t="n">
-        <v>-0.0948</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J252" t="n">
-        <v>-2.1804</v>
+        <v>-1.8676</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>0.86</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.1756</v>
+        <v>-0.1589</v>
       </c>
       <c r="J253" t="n">
-        <v>-4.0388</v>
+        <v>-3.6547</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.82</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.2162</v>
+        <v>-0.1986</v>
       </c>
       <c r="J254" t="n">
-        <v>-4.9726</v>
+        <v>-4.5678</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.77</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2637</v>
+        <v>-0.2457</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.0651</v>
+        <v>-5.6511</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.3383</v>
+        <v>-0.3226</v>
       </c>
       <c r="J256" t="n">
-        <v>-7.7809</v>
+        <v>-7.4198</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.71</v>
       </c>
       <c r="I257" t="n">
-        <v>1.361</v>
+        <v>1.3838</v>
       </c>
       <c r="J257" t="n">
-        <v>31.303</v>
+        <v>31.8274</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.34</v>
       </c>
       <c r="I258" t="n">
-        <v>0.8167</v>
+        <v>0.7974</v>
       </c>
       <c r="J258" t="n">
-        <v>18.7841</v>
+        <v>18.3402</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>1.34</v>
       </c>
       <c r="I259" t="n">
-        <v>0.8167</v>
+        <v>0.7974</v>
       </c>
       <c r="J259" t="n">
-        <v>18.7841</v>
+        <v>18.3402</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>1.31</v>
       </c>
       <c r="I260" t="n">
-        <v>0.7588</v>
+        <v>0.7365</v>
       </c>
       <c r="J260" t="n">
-        <v>17.4524</v>
+        <v>16.9395</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.76</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.7296</v>
+        <v>-0.7057</v>
       </c>
       <c r="J261" t="n">
-        <v>-16.7808</v>
+        <v>-16.2311</v>
       </c>
     </row>
   </sheetData>
